--- a/01. BaseTraining/unit11_Uboot/unit11_Uboot.xlsx
+++ b/01. BaseTraining/unit11_Uboot/unit11_Uboot.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="3"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Second stage boot loader." sheetId="3" r:id="rId2"/>
+    <sheet name="First-Second stage boot loader." sheetId="3" r:id="rId2"/>
     <sheet name="Third stage boot loader" sheetId="4" r:id="rId3"/>
     <sheet name="command line" sheetId="5" r:id="rId4"/>
     <sheet name="load Linux kernel" sheetId="7" r:id="rId5"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="236">
   <si>
     <t>protocall driver cho nokia 5110</t>
   </si>
@@ -62,8 +62,713 @@
     <t>Như vậy sau khi boot rom chạy xong nó sẽ nhảy đến câu lệnh đầu tiên được lưu trữ trên thẻ nhớ và đó chính là câu lệnh đầu tiên của MLO (second stage).</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Vị trí và vai trò của </t>
+    <t xml:space="preserve">  arch/arm/cpu/armv7/start.S</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mọi thao tác đều được thực hiện thông qua </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>các thanh ghi của CPU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc bộ nhớ tạm thời như SRAM (nếu có).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>start.S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> thực hiện các công việc khởi tạo cơ bản như:</t>
+    </r>
+  </si>
+  <si>
+    <t>Thiết lập chế độ hoạt động của CPU.</t>
+  </si>
+  <si>
+    <t>Vô hiệu hóa hoặc cấu hình các tính năng như cache, MMU (nếu cần).</t>
+  </si>
+  <si>
+    <t>Mục tiêu chính</t>
+  </si>
+  <si>
+    <t>make Uboot</t>
+  </si>
+  <si>
+    <t>#user@localhost:~/u-boot$</t>
+  </si>
+  <si>
+    <t>make ARCH=arm CROSS_COMPILE=${CC} distclean</t>
+  </si>
+  <si>
+    <t>make ARCH=arm CROSS_COMPILE=${CC} am335x_evm_defconfig</t>
+  </si>
+  <si>
+    <t>make ARCH=arm CROSS_COMPILE=${CC}</t>
+  </si>
+  <si>
+    <t>=&gt; việc lựa chọn đã được thực thi khi make Uboot</t>
+  </si>
+  <si>
+    <t>arch/arm/cpu/armv7/start.S.</t>
+  </si>
+  <si>
+    <t>mặc định đã được nạp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPU nhảy vào địa chỉ bắt đầu </t>
+  </si>
+  <si>
+    <t>ENTRY(...)</t>
+  </si>
+  <si>
+    <t>switch_to_hypervisor_ret:</t>
+  </si>
+  <si>
+    <t>bl _main</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>arch/arm/lib/crt0_64.S</t>
+  </si>
+  <si>
+    <t>ENTRY(_main)</t>
+  </si>
+  <si>
+    <t>Tạo stack ban đầu</t>
+  </si>
+  <si>
+    <t>Cấp phát và khởi tạo vùng gd (global data)</t>
+  </si>
+  <si>
+    <t>bl board_init_f</t>
+  </si>
+  <si>
+    <t>arch\arm\mach-omap2\hwinit-common.c</t>
+  </si>
+  <si>
+    <t>void board_init_f(ulong dummy)</t>
+  </si>
+  <si>
+    <t>b relocate_code</t>
+  </si>
+  <si>
+    <t>b  board_init_r</t>
+  </si>
+  <si>
+    <t>early_system_init();</t>
+  </si>
+  <si>
+    <t>board_early_init_f();</t>
+  </si>
+  <si>
+    <t>sdram_init();</t>
+  </si>
+  <si>
+    <t>gd-&gt;ram_size = omap_sdram_size();</t>
+  </si>
+  <si>
+    <t>common/spl/spl.c</t>
+  </si>
+  <si>
+    <t>void board_init_r(gd_t *dummy1, ulong dummy2)</t>
+  </si>
+  <si>
+    <t>jump_to_image_*(&amp;spl_image);</t>
+  </si>
+  <si>
+    <t>Khởi tạo thêm 1 số thứ nữa</t>
+  </si>
+  <si>
+    <t>Third stage boot loader</t>
+  </si>
+  <si>
+    <t>First stage boot loader</t>
+  </si>
+  <si>
+    <t>=&gt; Kết quả của quá trình build Uboot sẽ cho 2 file MLO(SPL) và u-boot.img, 2 file này là 2 lần build độc lập nên có thể có một số file, hàm giống nhau được phân biệt giữa 2 lần build bởi ifdefine</t>
+  </si>
+  <si>
+    <t>common\board_f.c</t>
+  </si>
+  <si>
+    <t>void board_init_f(ulong boot_flags)</t>
+  </si>
+  <si>
+    <t>static inline int initcall_run_list(const init_fnc_t init_sequence[])</t>
+  </si>
+  <si>
+    <t>ret = (*init_fnc_ptr)()</t>
+  </si>
+  <si>
+    <t>static int setup_mon_len(void)</t>
+  </si>
+  <si>
+    <t>common\board_r.c</t>
+  </si>
+  <si>
+    <t>void board_init_r(gd_t *new_gd, ulong dest_addr)</t>
+  </si>
+  <si>
+    <t>initcall_run_list(init_sequence_r)</t>
+  </si>
+  <si>
+    <t>include\initcall.h</t>
+  </si>
+  <si>
+    <t>static inline int initcall_run_list</t>
+  </si>
+  <si>
+    <t>(const init_fnc_t init_sequence[])</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>static int run_main_loop(void)</t>
+  </si>
+  <si>
+    <t>main_loop();</t>
+  </si>
+  <si>
+    <t>common\main.c</t>
+  </si>
+  <si>
+    <t>void main_loop(void)</t>
+  </si>
+  <si>
+    <t>common\autoboot.c</t>
+  </si>
+  <si>
+    <t>void autoboot_command(const char *s)</t>
+  </si>
+  <si>
+    <t>autoboot_command(s);</t>
+  </si>
+  <si>
+    <t>run_command_list(s, -1, 0);</t>
+  </si>
+  <si>
+    <t>for (;;)</t>
+  </si>
+  <si>
+    <t>1.2.3. Third stage boot loader</t>
+  </si>
+  <si>
+    <t>1.2.4. Hệ thống command line của u-boot</t>
+  </si>
+  <si>
+    <t>Trên Linux thì các command line bản chất là các file binary được đặt trong thư mục /bin hoặc /sbin của hệ thống.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuy nhiên do u-boot là một chương trình vi điều khiển, do vậy các command line của nó là các function trong source code. </t>
+  </si>
+  <si>
+    <t>Mỗi 1 function khi muốn đăng ký thành command line sẽ sử dụng macro U_BOOT_CMD giống như dưới:</t>
+  </si>
+  <si>
+    <t>      );</t>
+  </si>
+  <si>
+    <t>U_BOOT_CMD(</t>
+  </si>
+  <si>
+    <t>        hab_auth_img, 4, 0, do_authenticate_image,</t>
+  </si>
+  <si>
+    <t>        "authenticate image via HAB",</t>
+  </si>
+  <si>
+    <t>        "addr length ivt_offset\n"</t>
+  </si>
+  <si>
+    <t>        "addr - image hex address\n"</t>
+  </si>
+  <si>
+    <t>        "length - image hex length\n"SSGSSG</t>
+  </si>
+  <si>
+    <t>        "ivt_offset - hex offset of IVT in the image"</t>
+  </si>
+  <si>
+    <t>Hàm do_main_loop sẽ liên tục get input của user thông qua serial, từ đó detect được command line mà user gõ.</t>
+  </si>
+  <si>
+    <t>Nếu như quá trình boot không bị interrupt bởi input từ user thì hàm do_main_loop sẽ thực thi 1 loạt command line để execute Linux kernel. Quá trình này giống như chạy shell script.</t>
+  </si>
+  <si>
+    <t>1.2.5. Quá trình load Linux kernel</t>
+  </si>
+  <si>
+    <t>1.2.6. Tổ chức source code của u-boot.</t>
+  </si>
+  <si>
+    <t>s = bootdelay_process();</t>
+  </si>
+  <si>
+    <t>const char *bootdelay_process(void)</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>bootcount_inc();</t>
+  </si>
+  <si>
+    <t>s = env_get("bootdelay");</t>
+  </si>
+  <si>
+    <t>env\common.c</t>
+  </si>
+  <si>
+    <t>char *env_get(const char *name)</t>
+  </si>
+  <si>
+    <t>if (gd-&gt;flags &amp; GD_FLG_ENV_READY)</t>
+  </si>
+  <si>
+    <t>if (env_get_f(name, (char *)(gd-&gt;env_buf), sizeof(gd-&gt;env_buf)) &gt;= 0)</t>
+  </si>
+  <si>
+    <t>return (char *)(gd-&gt;env_buf);</t>
+  </si>
+  <si>
+    <r>
+      <t>hsearch_r(e, ENV_FIND, &amp;ep, &amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env_htab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 0);</t>
+    </r>
+  </si>
+  <si>
+    <t>return ep ? ep-&gt;data : NULL;</t>
+  </si>
+  <si>
+    <t>s = env_get("bootcmd");</t>
+  </si>
+  <si>
+    <t>bootdelay = s ? (int)simple_strtol(s, NULL, 10) : CONFIG_BOOTDELAY;</t>
+  </si>
+  <si>
+    <t>stored_bootdelay = bootdelay;</t>
+  </si>
+  <si>
+    <t>if (s &amp;&amp; (stored_bootdelay == -2 ||</t>
+  </si>
+  <si>
+    <t> (stored_bootdelay != -1 &amp;&amp; !abortboot(stored_bootdelay))))</t>
+  </si>
+  <si>
+    <t>common\cli.c</t>
+  </si>
+  <si>
+    <t>int run_command_list(const char *cmd, int len, int flag)</t>
+  </si>
+  <si>
+    <t>rcode = board_run_command(buff);</t>
+  </si>
+  <si>
+    <t>if (IS_ENABLED(CONFIG_AUTOBOOT_USE_MENUKEY) &amp;&amp;</t>
+  </si>
+  <si>
+    <t>menukey == AUTOBOOT_MENUKEY) {</t>
+  </si>
+  <si>
+    <t>s = env_get("menucmd");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. cmd: Chứa source code của tất cả các command line. Thông thường mỗi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">command line sẽ là 1 file source C. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. configs: Chứa file config để generate ra file .config khi build u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Documentation: Chứa hệ thống tài liệu của u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. env: Chứa source code để xây dựng ra hệ thống biến môi trương của u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. lib: Source code phần middler ware của u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. net: Source code liên quan đến tính năng network. U-boot cũng có thể sử dụng </t>
+  </si>
+  <si>
+    <t xml:space="preserve">được network như ping, sftp,… </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. arch: Source code specific cho từng platform. Device tree cũng được lưu trữ trong </t>
+  </si>
+  <si>
+    <t xml:space="preserve">folder này. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. common: Source code phần middler ware của u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. drivers: Chứa source code driver của từng board. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. spl: Chứa 1 phần code để build ra second stage boot loader. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11. tools: Chứa các loại tool dùng trong quá trình build u-boot. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12. fs: Chứa source code của các loại file system dùng trong u-boot. U-boot cũng </t>
+  </si>
+  <si>
+    <t>có tính năng đọc file theo file name như Linux.</t>
+  </si>
+  <si>
+    <t>load Linux kernel</t>
+  </si>
+  <si>
+    <t>initr_env</t>
+  </si>
+  <si>
+    <t>static int initr_env(void)</t>
+  </si>
+  <si>
+    <t>Quá trình Load Kernel Image</t>
+  </si>
+  <si>
+    <t>Đặc điểm chung:</t>
+  </si>
+  <si>
+    <t>Mỗi board có chuỗi command line riêng để load kernel image lên RAM</t>
+  </si>
+  <si>
+    <t>Các hãng sản xuất board tạo script riêng cho từng loại board</t>
+  </si>
+  <si>
+    <t>U-Boot thực thi script này mà không cần quan tâm chi tiết bên trong</t>
+  </si>
+  <si>
+    <t>Cấu hình Script:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Script được định nghĩa bằng macro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CONFIG_EXTRA_ENV_SETTINGS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nằm trong thư mục </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/include/configs</t>
+    </r>
+  </si>
+  <si>
+    <t>Quy trình cụ thể với Beagle Bone Black:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Đọc cấu hình:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> U-Boot đọc file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/boot/uEnv.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> từ SD card để lấy config hệ thống</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Load file:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Lựa chọn và load kernel image cùng DTB file từ MMC hoặc SD card lên RAM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Giải nén:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dựa vào định dạng kernel image (uImage hoặc zImage) để thực hiện giải nén</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Khởi động kernel:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gọi lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> với địa chỉ RAM của kernel image và DTB file</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>bootm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> jump đến instruction đầu tiên của kernel</t>
+    </r>
+  </si>
+  <si>
+    <t>Chuyển toàn bộ quyền điều khiển hệ thống cho kernel</t>
+  </si>
+  <si>
+    <r>
+      <t>Kết quả:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> U-Boot hoàn thành nhiệm vụ khởi tạo và chuyển giao quyền điều khiển cho Linux kernel.</t>
+    </r>
+  </si>
+  <si>
+    <t>=&gt; quá trình lấy chuỗi cmd được diễn giải qua trong sheet thỉd stage boot loader và command line, đây là nhắc lại chi tiết:</t>
+  </si>
+  <si>
+    <t>Lấy các biến môi trường tương ứng với board:</t>
+  </si>
+  <si>
+    <t>env_relocate();</t>
+  </si>
+  <si>
+    <t>void env_relocate(void)</t>
+  </si>
+  <si>
+    <t>env_load();</t>
+  </si>
+  <si>
+    <t>env\env.c</t>
+  </si>
+  <si>
+    <t>int env_load(void)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">for (prio = 0; (drv = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env_driver_lookup(ENVOP_LOAD, prio)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>); prio++)</t>
+    </r>
+  </si>
+  <si>
+    <t>static struct env_driver *env_driver_lookup(enum env_operation op, int prio)</t>
+  </si>
+  <si>
+    <t>__weak enum env_location env_get_location(enum env_operation op, int prio)</t>
+  </si>
+  <si>
+    <t>return env_locations[prio];</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">enum env_location loc = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>env_get_location</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(op, prio);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>drv =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> _env_driver_lookup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(loc);</t>
+    </r>
+  </si>
+  <si>
+    <t>= ENVL_MMC // nếu là BBB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ví dụ: Beagle Bone có file riêng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>include/configs/omap3_beagle.h</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🧩 Vai trò của </t>
     </r>
     <r>
       <rPr>
@@ -72,16 +777,248 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>start.S</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">File </t>
+      <t>U_BOOT_CMD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> trong autoboot</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">    bootm, CONFIG_SYS_MAXARGS, 1, do_bootm,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Boot application image from memory",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Usage: bootm &lt;addr&gt;"</t>
+  </si>
+  <si>
+    <t>);</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">➡️ Nếu lệnh không được đăng ký bằng </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>U_BOOT_CMD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, thì khi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootcmd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> gọi nó, U-Boot sẽ báo lỗi “Unknown command”.</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ 2. Tạo bảng lệnh (command table)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Macro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>U_BOOT_CMD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tạo ra một entry kiểu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cmd_tbl_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> và đặt nó vào một section đặc biệt trong bộ nhớ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi U-Boot khởi động, nó quét các entry này để xây dựng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>bảng lệnh nội bộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>autoboot_command()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> gọi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>run_command_list(getenv("bootcmd"))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, nó tra bảng này để thực thi từng lệnh.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đăng ký chuỗi cmd U_BOOT_CMD</t>
+  </si>
+  <si>
+    <t>VD:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">✅ 1. Đăng ký các lệnh mà </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootcmd</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ gọi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong U-Boot, các câu lệnh đầu tiên được thực thi nằm trong file hợp ngữ có tên là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>start.S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vị trí và vai trò của </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>start.S</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">File </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
@@ -98,21 +1035,40 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">  arch/arm/cpu/armv7/start.S</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Đặc điểm của </t>
+    <r>
+      <t xml:space="preserve">Mỗi loại vi xử lý (SoC) sẽ có phiên bản </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
       <t>start.S</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> riêng, được thiết kế phù hợp với đặc điểm phần cứng của chip đó. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đặc điểm của </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>start.S</t>
+    </r>
   </si>
   <si>
     <r>
@@ -120,7 +1076,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
@@ -157,55 +1113,11 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Mọi thao tác đều được thực hiện thông qua </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>các thanh ghi của CPU</t>
+      <t xml:space="preserve">Chuẩn bị môi trường để có thể gọi hàm C đầu tiên là </t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> hoặc bộ nhớ tạm thời như SRAM (nếu có).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>start.S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> thực hiện các công việc khởi tạo cơ bản như:</t>
-    </r>
-  </si>
-  <si>
-    <t>Thiết lập chế độ hoạt động của CPU.</t>
-  </si>
-  <si>
-    <t>Vô hiệu hóa hoặc cấu hình các tính năng như cache, MMU (nếu cần).</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Chuẩn bị môi trường để có thể gọi hàm C đầu tiên là </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
@@ -222,15 +1134,12 @@
     </r>
   </si>
   <si>
-    <t>Mục tiêu chính</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Mục tiêu của </t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
@@ -266,7 +1175,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
@@ -283,931 +1192,442 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Trong U-Boot, các câu lệnh đầu tiên được thực thi nằm trong file hợp ngữ có tên là </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>start.S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mỗi loại vi xử lý (SoC) sẽ có phiên bản </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>start.S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> riêng, được thiết kế phù hợp với đặc điểm phần cứng của chip đó. </t>
-    </r>
-  </si>
-  <si>
-    <t>make Uboot</t>
-  </si>
-  <si>
-    <t>#user@localhost:~/u-boot$</t>
-  </si>
-  <si>
-    <t>make ARCH=arm CROSS_COMPILE=${CC} distclean</t>
-  </si>
-  <si>
-    <t>make ARCH=arm CROSS_COMPILE=${CC} am335x_evm_defconfig</t>
-  </si>
-  <si>
-    <t>make ARCH=arm CROSS_COMPILE=${CC}</t>
-  </si>
-  <si>
-    <t>=&gt; việc lựa chọn đã được thực thi khi make Uboot</t>
-  </si>
-  <si>
-    <t>arch/arm/cpu/armv7/start.S.</t>
-  </si>
-  <si>
-    <t>mặc định đã được nạp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPU nhảy vào địa chỉ bắt đầu </t>
-  </si>
-  <si>
-    <t>ENTRY(...)</t>
-  </si>
-  <si>
-    <t>switch_to_hypervisor_ret:</t>
-  </si>
-  <si>
-    <t>bl _main</t>
-  </si>
-  <si>
-    <t>…</t>
-  </si>
-  <si>
-    <t>arch/arm/lib/crt0_64.S</t>
-  </si>
-  <si>
-    <t>ENTRY(_main)</t>
-  </si>
-  <si>
-    <t>Tạo stack ban đầu</t>
-  </si>
-  <si>
-    <t>Cấp phát và khởi tạo vùng gd (global data)</t>
-  </si>
-  <si>
-    <t>bl board_init_f</t>
-  </si>
-  <si>
-    <t>arch\arm\mach-omap2\hwinit-common.c</t>
-  </si>
-  <si>
-    <t>void board_init_f(ulong dummy)</t>
-  </si>
-  <si>
-    <t>b relocate_code</t>
-  </si>
-  <si>
-    <t>b  board_init_r</t>
-  </si>
-  <si>
-    <t>early_system_init();</t>
-  </si>
-  <si>
-    <t>board_early_init_f();</t>
-  </si>
-  <si>
-    <t>sdram_init();</t>
-  </si>
-  <si>
-    <t>gd-&gt;ram_size = omap_sdram_size();</t>
-  </si>
-  <si>
-    <t>common/spl/spl.c</t>
-  </si>
-  <si>
-    <t>void board_init_r(gd_t *dummy1, ulong dummy2)</t>
-  </si>
-  <si>
-    <t>jump_to_image_*(&amp;spl_image);</t>
-  </si>
-  <si>
-    <t>Khởi tạo thêm 1 số thứ nữa</t>
-  </si>
-  <si>
-    <t>Third stage boot loader</t>
-  </si>
-  <si>
-    <t>First stage boot loader</t>
-  </si>
-  <si>
-    <t>=&gt; Kết quả của quá trình build Uboot sẽ cho 2 file MLO(SPL) và u-boot.img, 2 file này là 2 lần build độc lập nên có thể có một số file, hàm giống nhau được phân biệt giữa 2 lần build bởi ifdefine</t>
-  </si>
-  <si>
-    <t>common\board_f.c</t>
-  </si>
-  <si>
-    <t>void board_init_f(ulong boot_flags)</t>
-  </si>
-  <si>
-    <t>static inline int initcall_run_list(const init_fnc_t init_sequence[])</t>
-  </si>
-  <si>
-    <t>ret = (*init_fnc_ptr)()</t>
-  </si>
-  <si>
-    <t>static int setup_mon_len(void)</t>
-  </si>
-  <si>
-    <t>common\board_r.c</t>
-  </si>
-  <si>
-    <t>void board_init_r(gd_t *new_gd, ulong dest_addr)</t>
-  </si>
-  <si>
-    <t>initcall_run_list(init_sequence_r)</t>
-  </si>
-  <si>
-    <t>include\initcall.h</t>
-  </si>
-  <si>
-    <t>static inline int initcall_run_list</t>
-  </si>
-  <si>
-    <t>(const init_fnc_t init_sequence[])</t>
-  </si>
-  <si>
-    <t>`</t>
-  </si>
-  <si>
-    <t>static int run_main_loop(void)</t>
-  </si>
-  <si>
-    <t>main_loop();</t>
-  </si>
-  <si>
-    <t>common\main.c</t>
-  </si>
-  <si>
-    <t>void main_loop(void)</t>
-  </si>
-  <si>
-    <t>common\autoboot.c</t>
-  </si>
-  <si>
-    <t>void autoboot_command(const char *s)</t>
-  </si>
-  <si>
-    <t>autoboot_command(s);</t>
-  </si>
-  <si>
-    <t>run_command_list(s, -1, 0);</t>
-  </si>
-  <si>
-    <t>for (;;)</t>
-  </si>
-  <si>
-    <t>1.2.3. Third stage boot loader</t>
-  </si>
-  <si>
-    <t>1.2.4. Hệ thống command line của u-boot</t>
-  </si>
-  <si>
-    <t>Trên Linux thì các command line bản chất là các file binary được đặt trong thư mục /bin hoặc /sbin của hệ thống.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuy nhiên do u-boot là một chương trình vi điều khiển, do vậy các command line của nó là các function trong source code. </t>
-  </si>
-  <si>
-    <t>Mỗi 1 function khi muốn đăng ký thành command line sẽ sử dụng macro U_BOOT_CMD giống như dưới:</t>
-  </si>
-  <si>
-    <t>      );</t>
-  </si>
-  <si>
-    <t>U_BOOT_CMD(</t>
-  </si>
-  <si>
-    <t>        hab_auth_img, 4, 0, do_authenticate_image,</t>
-  </si>
-  <si>
-    <t>        "authenticate image via HAB",</t>
-  </si>
-  <si>
-    <t>        "addr length ivt_offset\n"</t>
-  </si>
-  <si>
-    <t>        "addr - image hex address\n"</t>
-  </si>
-  <si>
-    <t>        "length - image hex length\n"SSGSSG</t>
-  </si>
-  <si>
-    <t>        "ivt_offset - hex offset of IVT in the image"</t>
-  </si>
-  <si>
-    <t>Hàm do_main_loop sẽ liên tục get input của user thông qua serial, từ đó detect được command line mà user gõ.</t>
-  </si>
-  <si>
-    <t>Nếu như quá trình boot không bị interrupt bởi input từ user thì hàm do_main_loop sẽ thực thi 1 loạt command line để execute Linux kernel. Quá trình này giống như chạy shell script.</t>
-  </si>
-  <si>
-    <t>1.2.5. Quá trình load Linux kernel</t>
-  </si>
-  <si>
-    <t>1.2.6. Tổ chức source code của u-boot.</t>
-  </si>
-  <si>
-    <t>s = bootdelay_process();</t>
-  </si>
-  <si>
-    <t>const char *bootdelay_process(void)</t>
-  </si>
-  <si>
-    <t>...</t>
-  </si>
-  <si>
-    <t>bootcount_inc();</t>
-  </si>
-  <si>
-    <t>s = env_get("bootdelay");</t>
-  </si>
-  <si>
-    <t>env\common.c</t>
-  </si>
-  <si>
-    <t>char *env_get(const char *name)</t>
-  </si>
-  <si>
-    <t>if (gd-&gt;flags &amp; GD_FLG_ENV_READY)</t>
-  </si>
-  <si>
-    <t>if (env_get_f(name, (char *)(gd-&gt;env_buf), sizeof(gd-&gt;env_buf)) &gt;= 0)</t>
-  </si>
-  <si>
-    <t>return (char *)(gd-&gt;env_buf);</t>
-  </si>
-  <si>
-    <r>
-      <t>hsearch_r(e, ENV_FIND, &amp;ep, &amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>env_htab</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, 0);</t>
-    </r>
-  </si>
-  <si>
-    <t>return ep ? ep-&gt;data : NULL;</t>
-  </si>
-  <si>
-    <t>s = env_get("bootcmd");</t>
-  </si>
-  <si>
-    <t>bootdelay = s ? (int)simple_strtol(s, NULL, 10) : CONFIG_BOOTDELAY;</t>
-  </si>
-  <si>
-    <t>stored_bootdelay = bootdelay;</t>
-  </si>
-  <si>
-    <t>if (s &amp;&amp; (stored_bootdelay == -2 ||</t>
-  </si>
-  <si>
-    <t> (stored_bootdelay != -1 &amp;&amp; !abortboot(stored_bootdelay))))</t>
-  </si>
-  <si>
-    <t>common\cli.c</t>
-  </si>
-  <si>
-    <t>int run_command_list(const char *cmd, int len, int flag)</t>
-  </si>
-  <si>
-    <t>rcode = board_run_command(buff);</t>
-  </si>
-  <si>
-    <t>if (IS_ENABLED(CONFIG_AUTOBOOT_USE_MENUKEY) &amp;&amp;</t>
-  </si>
-  <si>
-    <t>menukey == AUTOBOOT_MENUKEY) {</t>
-  </si>
-  <si>
-    <t>s = env_get("menucmd");</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. cmd: Chứa source code của tất cả các command line. Thông thường mỗi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">command line sẽ là 1 file source C. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. configs: Chứa file config để generate ra file .config khi build u-boot. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Documentation: Chứa hệ thống tài liệu của u-boot. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. env: Chứa source code để xây dựng ra hệ thống biến môi trương của u-boot. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. lib: Source code phần middler ware của u-boot. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. net: Source code liên quan đến tính năng network. U-boot cũng có thể sử dụng </t>
-  </si>
-  <si>
-    <t xml:space="preserve">được network như ping, sftp,… </t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. arch: Source code specific cho từng platform. Device tree cũng được lưu trữ trong </t>
-  </si>
-  <si>
-    <t xml:space="preserve">folder này. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. common: Source code phần middler ware của u-boot. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. drivers: Chứa source code driver của từng board. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. spl: Chứa 1 phần code để build ra second stage boot loader. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. tools: Chứa các loại tool dùng trong quá trình build u-boot. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12. fs: Chứa source code của các loại file system dùng trong u-boot. U-boot cũng </t>
-  </si>
-  <si>
-    <t>có tính năng đọc file theo file name như Linux.</t>
-  </si>
-  <si>
-    <t>load Linux kernel</t>
-  </si>
-  <si>
-    <t>initr_env</t>
-  </si>
-  <si>
-    <t>static int initr_env(void)</t>
-  </si>
-  <si>
-    <t>Quá trình Load Kernel Image</t>
-  </si>
-  <si>
-    <t>Đặc điểm chung:</t>
-  </si>
-  <si>
-    <t>Mỗi board có chuỗi command line riêng để load kernel image lên RAM</t>
-  </si>
-  <si>
-    <t>Các hãng sản xuất board tạo script riêng cho từng loại board</t>
-  </si>
-  <si>
-    <t>U-Boot thực thi script này mà không cần quan tâm chi tiết bên trong</t>
-  </si>
-  <si>
-    <t>Cấu hình Script:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Script được định nghĩa bằng macro </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>CONFIG_EXTRA_ENV_SETTINGS</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Nằm trong thư mục </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>/include/configs</t>
-    </r>
-  </si>
-  <si>
-    <t>Quy trình cụ thể với Beagle Bone Black:</t>
-  </si>
-  <si>
-    <r>
-      <t>1. Đọc cấu hình:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> U-Boot đọc file </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>/boot/uEnv.txt</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> từ SD card để lấy config hệ thống</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. Load file:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Lựa chọn và load kernel image cùng DTB file từ MMC hoặc SD card lên RAM</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3. Giải nén:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Dựa vào định dạng kernel image (uImage hoặc zImage) để thực hiện giải nén</t>
-    </r>
-  </si>
-  <si>
-    <t>4. Khởi động kernel:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Gọi lệnh </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>bootm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> với địa chỉ RAM của kernel image và DTB file</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>bootm</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> jump đến instruction đầu tiên của kernel</t>
-    </r>
-  </si>
-  <si>
-    <t>Chuyển toàn bộ quyền điều khiển hệ thống cho kernel</t>
-  </si>
-  <si>
-    <r>
-      <t>Kết quả:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> U-Boot hoàn thành nhiệm vụ khởi tạo và chuyển giao quyền điều khiển cho Linux kernel.</t>
-    </r>
-  </si>
-  <si>
-    <t>=&gt; quá trình lấy chuỗi cmd được diễn giải qua trong sheet thỉd stage boot loader và command line, đây là nhắc lại chi tiết:</t>
-  </si>
-  <si>
-    <t>Lấy các biến môi trường tương ứng với board:</t>
-  </si>
-  <si>
-    <t>env_relocate();</t>
-  </si>
-  <si>
-    <t>void env_relocate(void)</t>
-  </si>
-  <si>
-    <t>env_load();</t>
-  </si>
-  <si>
-    <t>env\env.c</t>
-  </si>
-  <si>
-    <t>int env_load(void)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">for (prio = 0; (drv = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>env_driver_lookup(ENVOP_LOAD, prio)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>); prio++)</t>
-    </r>
-  </si>
-  <si>
-    <t>static struct env_driver *env_driver_lookup(enum env_operation op, int prio)</t>
-  </si>
-  <si>
-    <t>__weak enum env_location env_get_location(enum env_operation op, int prio)</t>
-  </si>
-  <si>
-    <t>return env_locations[prio];</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">enum env_location loc = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>env_get_location</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(op, prio);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>drv =</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> _env_driver_lookup</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(loc);</t>
-    </r>
-  </si>
-  <si>
-    <t>= ENVL_MMC // nếu là BBB</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ví dụ: Beagle Bone có file riêng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>include/configs/omap3_beagle.h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">🧩 Vai trò của </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>U_BOOT_CMD</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> trong autoboot</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">    bootm, CONFIG_SYS_MAXARGS, 1, do_bootm,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    "Boot application image from memory",</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    "Usage: bootm &lt;addr&gt;"</t>
-  </si>
-  <si>
-    <t>);</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">➡️ Nếu lệnh không được đăng ký bằng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>U_BOOT_CMD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, thì khi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>bootcmd</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> gọi nó, U-Boot sẽ báo lỗi “Unknown command”.</t>
-    </r>
-  </si>
-  <si>
-    <t>✅ 2. Tạo bảng lệnh (command table)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Macro </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>U_BOOT_CMD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tạo ra một entry kiểu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>cmd_tbl_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> và đặt nó vào một section đặc biệt trong bộ nhớ.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Khi U-Boot khởi động, nó quét các entry này để xây dựng </t>
+    <t>Vai trò chính:</t>
+  </si>
+  <si>
+    <t>Vị trí trong Boot Chain:</t>
+  </si>
+  <si>
+    <t>Power On → First Stage Bootloader (Boot ROM) → Second Stage Bootloader (U-Boot/SPL) → Kernel → Rootfs</t>
+  </si>
+  <si>
+    <t>2. Đặc điểm của First Stage Boot Loader</t>
+  </si>
+  <si>
+    <t>A. Đặc điểm Phần Cứng</t>
+  </si>
+  <si>
+    <t>Vị trí lưu trữ:</t>
+  </si>
+  <si>
+    <t>Tài nguyên giới hạn:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kích thước rất nhỏ: </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Arial"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>bảng lệnh nội bộ</t>
+      <t>4KB - 128KB</t>
+    </r>
+  </si>
+  <si>
+    <t>Không có OS, chạy bare-metal</t>
+  </si>
+  <si>
+    <t>Khả năng truy cập phần cứng:</t>
+  </si>
+  <si>
+    <t>CPU core, clock tree cơ bản</t>
+  </si>
+  <si>
+    <t>GPIO (tối thiểu)</t>
+  </si>
+  <si>
+    <t>Một số interface boot: UART, SPI, I2C, USB, eMMC, SD/MMC</t>
+  </si>
+  <si>
+    <t>B. Đặc điểm Phần Mềm</t>
+  </si>
+  <si>
+    <t>Chức năng cốt lõi:</t>
+  </si>
+  <si>
+    <t>Hạn chế:</t>
+  </si>
+  <si>
+    <t>✗ Không có filesystem support</t>
+  </si>
+  <si>
+    <t>✗ Không có network stack</t>
+  </si>
+  <si>
+    <t>✗ Không có debug interface phức tạp</t>
+  </si>
+  <si>
+    <t>✗ Code phải cực kỳ tối ưu về kích thước</t>
+  </si>
+  <si>
+    <t>3. Ví dụ với Các Hãng Phổ Biến</t>
+  </si>
+  <si>
+    <t>Đặc điểm phần cứng:</t>
+  </si>
+  <si>
+    <t>Đặc điểm phần mềm:</t>
+  </si>
+  <si>
+    <t>Boot ROM: ~176KB</t>
+  </si>
+  <si>
+    <t>SRAM: 128KB (AM335x) - 256KB (AM62x)</t>
+  </si>
+  <si>
+    <t>Boot sources: MMC, NAND, SPI, UART, USB, Ethernet</t>
+  </si>
+  <si>
+    <t>GP header (General Purpose) cho non-secure</t>
+  </si>
+  <si>
+    <t>Signed image cho HS (High Security) devices</t>
+  </si>
+  <si>
+    <r>
+      <t>Khởi tạo cơ bản phần cứng</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Arial"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Khi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>autoboot_command()</t>
+      <t>: CPU, clock, một phần RAM tối thiểu</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tìm và nạp Second Stage Bootloader</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Arial"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> gọi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>run_command_list(getenv("bootcmd"))</t>
+      <t xml:space="preserve"> (như U-Boot) từ bộ nhớ ngoài (NAND, eMMC, SD card, NOR flash)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Xác thực tính toàn vẹn</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Segoe UI"/>
+        <rFont val="Arial"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>, nó tra bảng này để thực thi từng lệnh.</t>
-    </r>
-  </si>
-  <si>
-    <t>Đăng ký chuỗi cmd U_BOOT_CMD</t>
-  </si>
-  <si>
-    <t>VD:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">✅ 1. Đăng ký các lệnh mà </t>
+      <t xml:space="preserve"> của code (nếu có secure boot)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Chuyển quyền điều khiển</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sang bootloader thứ 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Boot ROM (mask ROM)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Code được ghi cố định tại nhà máy, không thể thay đổi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>OTP (One-Time Programmable) memory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Có thể ghi một lần duy nhất</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>eFuse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Dùng cho secure boot keys</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chỉ dùng </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial Unicode MS"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t>bootcmd</t>
+      <t>on-chip SRAM</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="13.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Segoe UI"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> sẽ gọi</t>
-    </r>
+      <t xml:space="preserve"> (chưa có DRAM)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. CPU &amp; Clock init</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Cấu hình PLL, đồng hồ hệ thống</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Memory init</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Khởi tạo SRAM controller</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Boot device detection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Xác định nguồn boot (SD, eMMC, NAND, USB...)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Load SPL/U-Boot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Copy code từ boot device vào RAM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Image verification</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kiểm tra checksum/signature (nếu secure boot)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. Jump to SPL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Nhảy đến địa chỉ thực thi của bootloader stage 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tên gọi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ROM Boot Loader (RBL)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Boot modes được xác định bởi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: SYSBOOT pins</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Memory-mapped boot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Tìm kiếm MLO (MMC/SD Linux Loader - SPL của U-Boot)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Image format</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fallback mechanism</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Tự động thử các boot source khác nhau theo thứ tự</t>
+    </r>
+  </si>
+  <si>
+    <t>First Stage Boot Loader</t>
+  </si>
+  <si>
+    <r>
+      <t>First Stage Boot Loader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (hay còn gọi là Primary Bootloader, Boot ROM) </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">là đoạn code khởi động đầu tiên được thực thi khi một hệ thống embedded bật nguồn. </t>
+  </si>
+  <si>
+    <t>Đây là thành phần quan trọng nhất trong chuỗi boot process.</t>
+  </si>
+  <si>
+    <t>Texas Instruments (Sitara AM335x, AM62x)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1215,7 +1635,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1257,15 +1677,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial Unicode MS"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1273,14 +1688,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="9"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1288,7 +1703,7 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1296,7 +1711,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1305,7 +1720,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -1314,21 +1729,21 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF002060"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1341,7 +1756,7 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1363,6 +1778,29 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
@@ -1576,7 +2014,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1618,22 +2056,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1647,23 +2080,23 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1680,25 +2113,25 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1709,6 +2142,71 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1733,13 +2231,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1786,13 +2284,13 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1839,13 +2337,13 @@
     <xdr:from>
       <xdr:col>29</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1892,13 +2390,13 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>46</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1945,13 +2443,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2045,13 +2543,13 @@
     <xdr:from>
       <xdr:col>31</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>61</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2098,14 +2596,14 @@
     <xdr:from>
       <xdr:col>48</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>57</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2120,8 +2618,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9220200" y="10668000"/>
-          <a:ext cx="1990725" cy="990600"/>
+          <a:off x="11430000" y="10487025"/>
+          <a:ext cx="2247900" cy="1047750"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
@@ -2174,13 +2672,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2263,13 +2761,13 @@
     <xdr:from>
       <xdr:col>48</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>57</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2340,13 +2838,13 @@
     <xdr:from>
       <xdr:col>63</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>71</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -6589,7 +7087,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E11"/>
-  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" t="s">
@@ -6623,22 +7121,22 @@
     </row>
     <row r="8" spans="2:5">
       <c r="E8" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="E9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="E10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="E11" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -6648,658 +7146,875 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BZ64"/>
-  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:BZ95"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" width="3.125" style="88"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:57">
-      <c r="B1" t="s">
+    <row r="1" spans="1:45" s="122" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A1" s="126" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" ht="15">
+      <c r="A2" s="64" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45">
+      <c r="A3" s="88" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45">
+      <c r="A4" s="88" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:45" ht="15">
+      <c r="A5" s="123" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45" ht="15">
+      <c r="A6" s="120" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45" ht="15">
+      <c r="A7" s="120" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45" ht="15">
+      <c r="A8" s="120" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45" ht="15">
+      <c r="A9" s="120" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45" ht="15">
+      <c r="A11" s="123" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45">
+      <c r="B12" s="102" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:45" ht="15">
+      <c r="A14" s="123" t="s">
+        <v>187</v>
+      </c>
+      <c r="AS14" s="123" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:45" ht="15">
+      <c r="A15" s="123" t="s">
+        <v>188</v>
+      </c>
+      <c r="W15" s="123" t="s">
+        <v>197</v>
+      </c>
+      <c r="AS15" s="123" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45" ht="15">
+      <c r="A16" s="123" t="s">
+        <v>189</v>
+      </c>
+      <c r="W16" s="123" t="s">
+        <v>198</v>
+      </c>
+      <c r="AS16" s="64" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="1:45" ht="15">
+      <c r="A17" s="120" t="s">
+        <v>216</v>
+      </c>
+      <c r="W17" s="120" t="s">
+        <v>220</v>
+      </c>
+      <c r="AS17" s="64" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:45" ht="15">
+      <c r="A18" s="120" t="s">
+        <v>217</v>
+      </c>
+      <c r="W18" s="120" t="s">
+        <v>221</v>
+      </c>
+      <c r="AS18" s="124" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:45" ht="15">
+      <c r="A19" s="120" t="s">
+        <v>218</v>
+      </c>
+      <c r="W19" s="120" t="s">
+        <v>222</v>
+      </c>
+      <c r="AS19" s="124" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:45" ht="15">
+      <c r="W20" s="120" t="s">
+        <v>223</v>
+      </c>
+      <c r="AS20" s="124" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:45" ht="15">
+      <c r="A21" s="123" t="s">
+        <v>190</v>
+      </c>
+      <c r="W21" s="120" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:45" ht="15">
+      <c r="A22" s="124" t="s">
+        <v>191</v>
+      </c>
+      <c r="W22" s="120" t="s">
+        <v>225</v>
+      </c>
+      <c r="AS22" s="64" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" spans="1:45" ht="15">
+      <c r="A23" s="124" t="s">
+        <v>219</v>
+      </c>
+      <c r="AS23" s="120" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="24" spans="1:45" ht="15">
+      <c r="A24" s="124" t="s">
+        <v>192</v>
+      </c>
+      <c r="W24" s="123" t="s">
+        <v>199</v>
+      </c>
+      <c r="AS24" s="120" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25" spans="1:45" ht="15">
+      <c r="W25" s="124" t="s">
+        <v>200</v>
+      </c>
+      <c r="AS25" s="120" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:45" ht="15">
+      <c r="A26" s="123" t="s">
+        <v>193</v>
+      </c>
+      <c r="W26" s="124" t="s">
+        <v>201</v>
+      </c>
+      <c r="AS26" s="125" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:45">
+      <c r="A27" s="124" t="s">
+        <v>194</v>
+      </c>
+      <c r="W27" s="124" t="s">
+        <v>202</v>
+      </c>
+      <c r="AS27" s="125" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:45" ht="15">
+      <c r="A28" s="124" t="s">
+        <v>195</v>
+      </c>
+      <c r="W28" s="124" t="s">
+        <v>203</v>
+      </c>
+      <c r="AS28" s="120" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:45">
+      <c r="A29" s="124" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" spans="1:45" ht="15" thickBot="1"/>
+    <row r="31" spans="1:45" s="122" customFormat="1" ht="15" thickBot="1">
+      <c r="A31" s="121"/>
+    </row>
+    <row r="32" spans="1:45">
+      <c r="B32" s="88" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:57">
-      <c r="B3" t="s">
+    <row r="34" spans="1:57">
+      <c r="B34" s="88" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:57">
-      <c r="C4" s="13" t="s">
+    <row r="35" spans="1:57">
+      <c r="C35" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-    </row>
-    <row r="5" spans="1:57">
-      <c r="C5" s="15" t="s">
+      <c r="D35" s="90"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="90"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="90"/>
+      <c r="M35" s="90"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="90"/>
+      <c r="P35" s="90"/>
+      <c r="Q35" s="90"/>
+      <c r="R35" s="90"/>
+      <c r="S35" s="90"/>
+      <c r="T35" s="90"/>
+      <c r="U35" s="90"/>
+      <c r="V35" s="90"/>
+      <c r="W35" s="90"/>
+      <c r="X35" s="90"/>
+    </row>
+    <row r="36" spans="1:57">
+      <c r="C36" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-    </row>
-    <row r="6" spans="1:57">
-      <c r="B6" t="s">
+      <c r="D36" s="92"/>
+      <c r="E36" s="92"/>
+      <c r="F36" s="92"/>
+      <c r="G36" s="92"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
+      <c r="J36" s="92"/>
+      <c r="K36" s="92"/>
+      <c r="L36" s="92"/>
+      <c r="M36" s="92"/>
+      <c r="N36" s="92"/>
+      <c r="O36" s="92"/>
+      <c r="P36" s="92"/>
+      <c r="Q36" s="92"/>
+      <c r="R36" s="92"/>
+      <c r="S36" s="92"/>
+      <c r="T36" s="92"/>
+      <c r="U36" s="92"/>
+      <c r="V36" s="92"/>
+      <c r="W36" s="92"/>
+      <c r="X36" s="92"/>
+    </row>
+    <row r="37" spans="1:57">
+      <c r="B37" s="88" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:57" ht="15.75" thickBot="1">
-      <c r="B7" t="s">
+    <row r="38" spans="1:57" ht="15" thickBot="1">
+      <c r="B38" s="88" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:57" s="27" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A8" s="26"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-    </row>
-    <row r="9" spans="1:57" ht="15.75" thickBot="1"/>
-    <row r="10" spans="1:57" ht="15.75" thickBot="1">
-      <c r="B10" s="29" t="s">
+    <row r="39" spans="1:57" s="94" customFormat="1" ht="15" thickBot="1">
+      <c r="A39" s="93"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="95"/>
+    </row>
+    <row r="40" spans="1:57" ht="15" thickBot="1"/>
+    <row r="41" spans="1:57" ht="15" thickBot="1">
+      <c r="B41" s="96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="97"/>
+      <c r="D41" s="97"/>
+      <c r="E41" s="97"/>
+      <c r="F41" s="97"/>
+      <c r="G41" s="97"/>
+      <c r="H41" s="97"/>
+      <c r="I41" s="98"/>
+    </row>
+    <row r="42" spans="1:57">
+      <c r="C42" s="88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" spans="1:57">
+      <c r="C43" s="88" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:57">
+      <c r="C44" s="88" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:57">
+      <c r="C45" s="88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:57" ht="15">
+      <c r="D47" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="99"/>
+      <c r="F47" s="99"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="99"/>
+      <c r="I47" s="99"/>
+      <c r="J47" s="99"/>
+      <c r="K47" s="99"/>
+      <c r="L47" s="99"/>
+      <c r="M47" s="99"/>
+      <c r="N47" s="99"/>
+      <c r="O47" s="99"/>
+      <c r="P47" s="99"/>
+      <c r="Q47" s="99"/>
+      <c r="R47" s="99"/>
+      <c r="S47" s="99"/>
+      <c r="T47" s="99"/>
+      <c r="U47" s="99"/>
+      <c r="V47" s="99"/>
+      <c r="W47" s="99"/>
+      <c r="X47" s="99"/>
+      <c r="Y47" s="99"/>
+      <c r="Z47" s="99"/>
+      <c r="AA47" s="99"/>
+      <c r="AB47" s="99"/>
+      <c r="AC47" s="99"/>
+      <c r="AD47" s="99"/>
+      <c r="AE47" s="99"/>
+      <c r="AF47" s="99"/>
+      <c r="AG47" s="99"/>
+      <c r="AH47" s="99"/>
+      <c r="AI47" s="99"/>
+      <c r="AJ47" s="99"/>
+      <c r="AK47" s="99"/>
+      <c r="AL47" s="99"/>
+      <c r="AM47" s="99"/>
+      <c r="AN47" s="99"/>
+      <c r="AO47" s="99"/>
+      <c r="AP47" s="99"/>
+      <c r="AQ47" s="99"/>
+      <c r="AR47" s="99"/>
+      <c r="AS47" s="99"/>
+      <c r="AT47" s="99"/>
+      <c r="AU47" s="99"/>
+      <c r="AV47" s="99"/>
+      <c r="AW47" s="99"/>
+      <c r="AX47" s="99"/>
+      <c r="AY47" s="99"/>
+      <c r="AZ47" s="99"/>
+      <c r="BA47" s="99"/>
+      <c r="BB47" s="99"/>
+      <c r="BC47" s="99"/>
+      <c r="BD47" s="99"/>
+      <c r="BE47" s="100"/>
+    </row>
+    <row r="48" spans="1:57" ht="15" thickBot="1"/>
+    <row r="49" spans="1:53" s="94" customFormat="1" ht="15" thickBot="1">
+      <c r="A49" s="93"/>
+    </row>
+    <row r="50" spans="1:53" ht="16.5">
+      <c r="C50" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+    </row>
+    <row r="51" spans="1:53" ht="16.5">
+      <c r="C51" s="101" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51" s="101"/>
+      <c r="E51" s="101"/>
+      <c r="F51" s="101"/>
+      <c r="G51" s="101"/>
+    </row>
+    <row r="52" spans="1:53" ht="16.5">
+      <c r="H52" s="20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="53" spans="1:53">
+      <c r="H53" s="102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:53" ht="16.5">
+      <c r="H54" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AM54" s="103" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN54" s="104"/>
+      <c r="AO54" s="104"/>
+      <c r="AP54" s="104"/>
+      <c r="AQ54" s="104"/>
+      <c r="AR54" s="104"/>
+      <c r="AS54" s="104"/>
+      <c r="AT54" s="104"/>
+      <c r="AU54" s="104"/>
+      <c r="AV54" s="104"/>
+      <c r="AW54" s="104"/>
+      <c r="AX54" s="104"/>
+      <c r="AY54" s="104"/>
+      <c r="AZ54" s="104"/>
+      <c r="BA54" s="104"/>
+    </row>
+    <row r="55" spans="1:53">
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="105"/>
+    </row>
+    <row r="56" spans="1:53" ht="16.5">
+      <c r="C56" s="101" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" s="101"/>
+      <c r="E56" s="101"/>
+      <c r="F56" s="101"/>
+      <c r="G56" s="101"/>
+    </row>
+    <row r="57" spans="1:53" ht="16.5">
+      <c r="C57" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+    </row>
+    <row r="58" spans="1:53" ht="16.5">
+      <c r="C58" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+    </row>
+    <row r="59" spans="1:53" ht="16.5">
+      <c r="C59" s="106" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="106"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="106"/>
+      <c r="G59" s="106"/>
+    </row>
+    <row r="60" spans="1:53" ht="16.5">
+      <c r="C60" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+    </row>
+    <row r="61" spans="1:53" ht="16.5">
+      <c r="C61" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+    </row>
+    <row r="62" spans="1:53" ht="16.5">
+      <c r="C62" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="23"/>
+    </row>
+    <row r="63" spans="1:53">
+      <c r="C63" s="105"/>
+      <c r="D63" s="105"/>
+      <c r="E63" s="105"/>
+      <c r="F63" s="105"/>
+      <c r="G63" s="105"/>
+    </row>
+    <row r="64" spans="1:53" ht="16.5">
+      <c r="C64" s="101" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="101"/>
+      <c r="E64" s="101"/>
+      <c r="F64" s="101"/>
+      <c r="G64" s="101"/>
+    </row>
+    <row r="65" spans="2:64" ht="16.5">
+      <c r="C65" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+    </row>
+    <row r="67" spans="2:64">
+      <c r="N67" s="107" t="s">
+        <v>24</v>
+      </c>
+      <c r="O67" s="108"/>
+      <c r="P67" s="108"/>
+      <c r="Q67" s="108"/>
+      <c r="R67" s="108"/>
+      <c r="S67" s="108"/>
+      <c r="T67" s="108"/>
+      <c r="U67" s="108"/>
+      <c r="V67" s="108"/>
+      <c r="W67" s="109"/>
+      <c r="Z67" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA67" s="108"/>
+      <c r="AB67" s="108"/>
+      <c r="AC67" s="108"/>
+      <c r="AD67" s="108"/>
+      <c r="AE67" s="108"/>
+      <c r="AF67" s="108"/>
+      <c r="AG67" s="109"/>
+      <c r="AO67" s="107" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP67" s="108"/>
+      <c r="AQ67" s="108"/>
+      <c r="AR67" s="108"/>
+      <c r="AS67" s="108"/>
+      <c r="AT67" s="108"/>
+      <c r="AU67" s="108"/>
+      <c r="AV67" s="108"/>
+      <c r="AW67" s="108"/>
+      <c r="AX67" s="108"/>
+      <c r="AY67" s="108"/>
+      <c r="AZ67" s="108"/>
+      <c r="BA67" s="109"/>
+      <c r="BG67" s="107" t="s">
+        <v>44</v>
+      </c>
+      <c r="BH67" s="108"/>
+      <c r="BI67" s="108"/>
+      <c r="BJ67" s="108"/>
+      <c r="BK67" s="108"/>
+      <c r="BL67" s="109"/>
+    </row>
+    <row r="68" spans="2:64">
+      <c r="R68" s="110"/>
+      <c r="AC68" s="110"/>
+      <c r="AT68" s="110"/>
+      <c r="BI68" s="111"/>
+    </row>
+    <row r="69" spans="2:64">
+      <c r="B69" s="112" t="s">
+        <v>49</v>
+      </c>
+      <c r="C69" s="99"/>
+      <c r="D69" s="99"/>
+      <c r="E69" s="99"/>
+      <c r="F69" s="99"/>
+      <c r="G69" s="99"/>
+      <c r="H69" s="100"/>
+      <c r="J69" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="31"/>
-    </row>
-    <row r="11" spans="1:57">
-      <c r="C11" t="s">
+      <c r="R69" s="110"/>
+      <c r="AC69" s="110"/>
+      <c r="AT69" s="110"/>
+      <c r="BI69" s="110"/>
+    </row>
+    <row r="70" spans="2:64">
+      <c r="J70" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="R70" s="110"/>
+      <c r="S70" s="88" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:57">
-      <c r="C12" t="s">
+      <c r="AC70" s="110"/>
+      <c r="AT70" s="110"/>
+      <c r="BI70" s="110"/>
+    </row>
+    <row r="71" spans="2:64">
+      <c r="R71" s="110"/>
+      <c r="S71" s="88" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC71" s="110"/>
+      <c r="AT71" s="110"/>
+      <c r="BI71" s="110"/>
+    </row>
+    <row r="72" spans="2:64">
+      <c r="R72" s="110"/>
+      <c r="S72" s="88" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:57">
-      <c r="C13" t="s">
+      <c r="AC72" s="110"/>
+      <c r="AT72" s="110"/>
+      <c r="BI72" s="110"/>
+    </row>
+    <row r="73" spans="2:64">
+      <c r="R73" s="110"/>
+      <c r="T73" s="88" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="1:57">
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:57">
-      <c r="D16" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="34"/>
-      <c r="W16" s="34"/>
-      <c r="X16" s="34"/>
-      <c r="Y16" s="34"/>
-      <c r="Z16" s="34"/>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="34"/>
-      <c r="AC16" s="34"/>
-      <c r="AD16" s="34"/>
-      <c r="AE16" s="34"/>
-      <c r="AF16" s="34"/>
-      <c r="AG16" s="34"/>
-      <c r="AH16" s="34"/>
-      <c r="AI16" s="34"/>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="34"/>
-      <c r="AL16" s="34"/>
-      <c r="AM16" s="34"/>
-      <c r="AN16" s="34"/>
-      <c r="AO16" s="34"/>
-      <c r="AP16" s="34"/>
-      <c r="AQ16" s="34"/>
-      <c r="AR16" s="34"/>
-      <c r="AS16" s="34"/>
-      <c r="AT16" s="34"/>
-      <c r="AU16" s="34"/>
-      <c r="AV16" s="34"/>
-      <c r="AW16" s="34"/>
-      <c r="AX16" s="34"/>
-      <c r="AY16" s="34"/>
-      <c r="AZ16" s="34"/>
-      <c r="BA16" s="34"/>
-      <c r="BB16" s="34"/>
-      <c r="BC16" s="34"/>
-      <c r="BD16" s="34"/>
-      <c r="BE16" s="35"/>
-    </row>
-    <row r="17" spans="1:53" ht="15.75" thickBot="1"/>
-    <row r="18" spans="1:53" s="27" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A18" s="26"/>
-    </row>
-    <row r="19" spans="1:53" ht="16.5">
-      <c r="C19" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-    </row>
-    <row r="20" spans="1:53" ht="21">
-      <c r="C20" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-    </row>
-    <row r="21" spans="1:53" ht="16.5">
-      <c r="H21" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:53">
-      <c r="H22" s="21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:53" ht="16.5">
-      <c r="H23" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM23" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="AN23" s="25"/>
-      <c r="AO23" s="25"/>
-      <c r="AP23" s="25"/>
-      <c r="AQ23" s="25"/>
-      <c r="AR23" s="25"/>
-      <c r="AS23" s="25"/>
-      <c r="AT23" s="25"/>
-      <c r="AU23" s="25"/>
-      <c r="AV23" s="25"/>
-      <c r="AW23" s="25"/>
-      <c r="AX23" s="25"/>
-      <c r="AY23" s="25"/>
-      <c r="AZ23" s="25"/>
-      <c r="BA23" s="25"/>
-    </row>
-    <row r="24" spans="1:53">
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-    </row>
-    <row r="25" spans="1:53" ht="21">
-      <c r="C25" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-    </row>
-    <row r="26" spans="1:53" ht="16.5">
-      <c r="C26" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-    </row>
-    <row r="27" spans="1:53" ht="16.5">
-      <c r="C27" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-    </row>
-    <row r="28" spans="1:53" ht="16.5">
-      <c r="C28" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-    </row>
-    <row r="29" spans="1:53" ht="16.5">
-      <c r="C29" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-    </row>
-    <row r="30" spans="1:53" ht="16.5">
-      <c r="C30" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-    </row>
-    <row r="31" spans="1:53" ht="16.5">
-      <c r="C31" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-    </row>
-    <row r="32" spans="1:53">
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-    </row>
-    <row r="33" spans="2:64" ht="21">
-      <c r="C33" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-    </row>
-    <row r="34" spans="2:64" ht="16.5">
-      <c r="C34" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-    </row>
-    <row r="36" spans="2:64">
-      <c r="N36" s="88" t="s">
+      <c r="AC73" s="110"/>
+      <c r="AD73" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="O36" s="89"/>
-      <c r="P36" s="89"/>
-      <c r="Q36" s="89"/>
-      <c r="R36" s="89"/>
-      <c r="S36" s="89"/>
-      <c r="T36" s="89"/>
-      <c r="U36" s="89"/>
-      <c r="V36" s="89"/>
-      <c r="W36" s="90"/>
-      <c r="Z36" s="88" t="s">
+      <c r="AT73" s="110"/>
+      <c r="BI73" s="110"/>
+    </row>
+    <row r="74" spans="2:64">
+      <c r="R74" s="110"/>
+      <c r="AC74" s="110"/>
+      <c r="AD74" s="113"/>
+      <c r="AE74" s="114"/>
+      <c r="AF74" s="114"/>
+      <c r="AG74" s="115"/>
+      <c r="AT74" s="110"/>
+      <c r="BI74" s="110"/>
+    </row>
+    <row r="75" spans="2:64">
+      <c r="R75" s="110"/>
+      <c r="AC75" s="110"/>
+      <c r="AE75" s="111"/>
+      <c r="AT75" s="110"/>
+      <c r="BI75" s="110"/>
+    </row>
+    <row r="76" spans="2:64">
+      <c r="R76" s="110"/>
+      <c r="AC76" s="110"/>
+      <c r="AE76" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT76" s="110"/>
+      <c r="BI76" s="110"/>
+    </row>
+    <row r="77" spans="2:64">
+      <c r="R77" s="110"/>
+      <c r="AC77" s="110"/>
+      <c r="AE77" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT77" s="110"/>
+      <c r="BI77" s="110"/>
+    </row>
+    <row r="78" spans="2:64">
+      <c r="R78" s="110"/>
+      <c r="AC78" s="110"/>
+      <c r="AE78" s="88" t="s">
+        <v>35</v>
+      </c>
+      <c r="AT78" s="110"/>
+      <c r="AU78" s="88" t="s">
+        <v>37</v>
+      </c>
+      <c r="BI78" s="110"/>
+    </row>
+    <row r="79" spans="2:64">
+      <c r="R79" s="110"/>
+      <c r="AC79" s="110"/>
+      <c r="AE79" s="110"/>
+      <c r="AT79" s="110"/>
+      <c r="AU79" s="113"/>
+      <c r="AV79" s="114"/>
+      <c r="AW79" s="114"/>
+      <c r="AX79" s="115"/>
+      <c r="BI79" s="110"/>
+    </row>
+    <row r="80" spans="2:64">
+      <c r="R80" s="110"/>
+      <c r="AC80" s="110"/>
+      <c r="AE80" s="110"/>
+      <c r="AT80" s="110"/>
+      <c r="AU80" s="116"/>
+      <c r="AV80" s="111"/>
+      <c r="BI80" s="110"/>
+    </row>
+    <row r="81" spans="18:78">
+      <c r="R81" s="110"/>
+      <c r="AC81" s="110"/>
+      <c r="AE81" s="88" t="s">
+        <v>38</v>
+      </c>
+      <c r="AT81" s="110"/>
+      <c r="AV81" s="110" t="s">
+        <v>40</v>
+      </c>
+      <c r="BI81" s="110"/>
+    </row>
+    <row r="82" spans="18:78">
+      <c r="R82" s="110"/>
+      <c r="AC82" s="110"/>
+      <c r="AE82" s="110"/>
+      <c r="AT82" s="110"/>
+      <c r="AV82" s="110" t="s">
+        <v>41</v>
+      </c>
+      <c r="BI82" s="110"/>
+    </row>
+    <row r="83" spans="18:78">
+      <c r="R83" s="110"/>
+      <c r="AC83" s="110"/>
+      <c r="AE83" s="110"/>
+      <c r="AT83" s="110"/>
+      <c r="AV83" s="110" t="s">
+        <v>42</v>
+      </c>
+      <c r="BI83" s="110"/>
+    </row>
+    <row r="84" spans="18:78">
+      <c r="R84" s="110"/>
+      <c r="AC84" s="110"/>
+      <c r="AE84" s="110"/>
+      <c r="AT84" s="110"/>
+      <c r="AV84" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="BI84" s="110"/>
+    </row>
+    <row r="85" spans="18:78">
+      <c r="R85" s="110"/>
+      <c r="AC85" s="110"/>
+      <c r="AE85" s="110"/>
+      <c r="AT85" s="110"/>
+      <c r="AU85" s="117"/>
+      <c r="AV85" s="118"/>
+      <c r="BI85" s="110"/>
+    </row>
+    <row r="86" spans="18:78">
+      <c r="R86" s="110"/>
+      <c r="AC86" s="110"/>
+      <c r="AE86" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="AA36" s="89"/>
-      <c r="AB36" s="89"/>
-      <c r="AC36" s="89"/>
-      <c r="AD36" s="89"/>
-      <c r="AE36" s="89"/>
-      <c r="AF36" s="89"/>
-      <c r="AG36" s="90"/>
-      <c r="AO36" s="88" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP36" s="89"/>
-      <c r="AQ36" s="89"/>
-      <c r="AR36" s="89"/>
-      <c r="AS36" s="89"/>
-      <c r="AT36" s="89"/>
-      <c r="AU36" s="89"/>
-      <c r="AV36" s="89"/>
-      <c r="AW36" s="89"/>
-      <c r="AX36" s="89"/>
-      <c r="AY36" s="89"/>
-      <c r="AZ36" s="89"/>
-      <c r="BA36" s="90"/>
-      <c r="BG36" s="88" t="s">
-        <v>52</v>
-      </c>
-      <c r="BH36" s="89"/>
-      <c r="BI36" s="89"/>
-      <c r="BJ36" s="89"/>
-      <c r="BK36" s="89"/>
-      <c r="BL36" s="90"/>
-    </row>
-    <row r="37" spans="2:64">
-      <c r="R37" s="6"/>
-      <c r="AC37" s="6"/>
-      <c r="AT37" s="6"/>
-      <c r="BI37" s="4"/>
-    </row>
-    <row r="38" spans="2:64">
-      <c r="B38" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="35"/>
-      <c r="J38" t="s">
-        <v>34</v>
-      </c>
-      <c r="R38" s="6"/>
-      <c r="AC38" s="6"/>
-      <c r="AT38" s="6"/>
-      <c r="BI38" s="6"/>
-    </row>
-    <row r="39" spans="2:64">
-      <c r="J39" t="s">
-        <v>33</v>
-      </c>
-      <c r="R39" s="6"/>
-      <c r="S39" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC39" s="6"/>
-      <c r="AT39" s="6"/>
-      <c r="BI39" s="6"/>
-    </row>
-    <row r="40" spans="2:64">
-      <c r="R40" s="6"/>
-      <c r="S40" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC40" s="6"/>
-      <c r="AT40" s="6"/>
-      <c r="BI40" s="6"/>
-    </row>
-    <row r="41" spans="2:64">
-      <c r="R41" s="6"/>
-      <c r="S41" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC41" s="6"/>
-      <c r="AT41" s="6"/>
-      <c r="BI41" s="6"/>
-    </row>
-    <row r="42" spans="2:64">
-      <c r="R42" s="6"/>
-      <c r="T42" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC42" s="6"/>
-      <c r="AD42" t="s">
-        <v>40</v>
-      </c>
-      <c r="AT42" s="6"/>
-      <c r="BI42" s="6"/>
-    </row>
-    <row r="43" spans="2:64">
-      <c r="R43" s="6"/>
-      <c r="AC43" s="6"/>
-      <c r="AD43" s="10"/>
-      <c r="AE43" s="11"/>
-      <c r="AF43" s="11"/>
-      <c r="AG43" s="12"/>
-      <c r="AT43" s="6"/>
-      <c r="BI43" s="6"/>
-    </row>
-    <row r="44" spans="2:64">
-      <c r="R44" s="6"/>
-      <c r="AC44" s="6"/>
-      <c r="AE44" s="4"/>
-      <c r="AT44" s="6"/>
-      <c r="BI44" s="6"/>
-    </row>
-    <row r="45" spans="2:64">
-      <c r="R45" s="6"/>
-      <c r="AC45" s="6"/>
-      <c r="AE45" t="s">
-        <v>41</v>
-      </c>
-      <c r="AT45" s="6"/>
-      <c r="BI45" s="6"/>
-    </row>
-    <row r="46" spans="2:64">
-      <c r="R46" s="6"/>
-      <c r="AC46" s="6"/>
-      <c r="AE46" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT46" s="6"/>
-      <c r="BI46" s="6"/>
-    </row>
-    <row r="47" spans="2:64">
-      <c r="R47" s="6"/>
-      <c r="AC47" s="6"/>
-      <c r="AE47" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT47" s="6"/>
-      <c r="AU47" t="s">
+      <c r="AT86" s="110"/>
+      <c r="BG86" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="BI47" s="6"/>
-    </row>
-    <row r="48" spans="2:64">
-      <c r="R48" s="6"/>
-      <c r="AC48" s="6"/>
-      <c r="AE48" s="6"/>
-      <c r="AT48" s="6"/>
-      <c r="AU48" s="10"/>
-      <c r="AV48" s="11"/>
-      <c r="AW48" s="11"/>
-      <c r="AX48" s="12"/>
-      <c r="BI48" s="6"/>
-    </row>
-    <row r="49" spans="18:78">
-      <c r="R49" s="6"/>
-      <c r="AC49" s="6"/>
-      <c r="AE49" s="6"/>
-      <c r="AT49" s="6"/>
-      <c r="AU49" s="2"/>
-      <c r="AV49" s="4"/>
-      <c r="BI49" s="6"/>
-    </row>
-    <row r="50" spans="18:78">
-      <c r="R50" s="6"/>
-      <c r="AC50" s="6"/>
-      <c r="AE50" t="s">
+      <c r="BI86" s="110"/>
+    </row>
+    <row r="87" spans="18:78">
+      <c r="R87" s="110"/>
+      <c r="AC87" s="110"/>
+      <c r="AE87" s="110"/>
+      <c r="AT87" s="110"/>
+      <c r="BI87" s="110"/>
+      <c r="BJ87" s="113"/>
+      <c r="BK87" s="114"/>
+      <c r="BL87" s="114"/>
+      <c r="BM87" s="115"/>
+    </row>
+    <row r="88" spans="18:78">
+      <c r="R88" s="110"/>
+      <c r="AC88" s="110"/>
+      <c r="AT88" s="110"/>
+      <c r="BI88" s="110"/>
+      <c r="BJ88" s="116"/>
+      <c r="BK88" s="111"/>
+    </row>
+    <row r="89" spans="18:78">
+      <c r="R89" s="110"/>
+      <c r="AC89" s="110"/>
+      <c r="AT89" s="110"/>
+      <c r="BI89" s="110"/>
+      <c r="BJ89" s="119"/>
+      <c r="BK89" s="88" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="18:78">
+      <c r="R90" s="110"/>
+      <c r="AC90" s="110"/>
+      <c r="AT90" s="110"/>
+      <c r="BI90" s="110"/>
+      <c r="BJ90" s="119"/>
+      <c r="BK90" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="AT50" s="6"/>
-      <c r="AV50" s="6" t="s">
+      <c r="BT90" s="112" t="s">
         <v>48</v>
       </c>
-      <c r="BI50" s="6"/>
-    </row>
-    <row r="51" spans="18:78">
-      <c r="R51" s="6"/>
-      <c r="AC51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AT51" s="6"/>
-      <c r="AV51" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="BI51" s="6"/>
-    </row>
-    <row r="52" spans="18:78">
-      <c r="R52" s="6"/>
-      <c r="AC52" s="6"/>
-      <c r="AE52" s="6"/>
-      <c r="AT52" s="6"/>
-      <c r="AV52" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="BI52" s="6"/>
-    </row>
-    <row r="53" spans="18:78">
-      <c r="R53" s="6"/>
-      <c r="AC53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AT53" s="6"/>
-      <c r="AV53" t="s">
-        <v>51</v>
-      </c>
-      <c r="BI53" s="6"/>
-    </row>
-    <row r="54" spans="18:78">
-      <c r="R54" s="6"/>
-      <c r="AC54" s="6"/>
-      <c r="AE54" s="6"/>
-      <c r="AT54" s="6"/>
-      <c r="AU54" s="7"/>
-      <c r="AV54" s="9"/>
-      <c r="BI54" s="6"/>
-    </row>
-    <row r="55" spans="18:78">
-      <c r="R55" s="6"/>
-      <c r="AC55" s="6"/>
-      <c r="AE55" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AT55" s="6"/>
-      <c r="BG55" t="s">
-        <v>53</v>
-      </c>
-      <c r="BI55" s="6"/>
-    </row>
-    <row r="56" spans="18:78">
-      <c r="R56" s="6"/>
-      <c r="AC56" s="6"/>
-      <c r="AE56" s="6"/>
-      <c r="AT56" s="6"/>
-      <c r="BI56" s="6"/>
-      <c r="BJ56" s="10"/>
-      <c r="BK56" s="11"/>
-      <c r="BL56" s="11"/>
-      <c r="BM56" s="12"/>
-    </row>
-    <row r="57" spans="18:78">
-      <c r="R57" s="6"/>
-      <c r="AC57" s="6"/>
-      <c r="AT57" s="6"/>
-      <c r="BI57" s="6"/>
-      <c r="BJ57" s="2"/>
-      <c r="BK57" s="4"/>
-    </row>
-    <row r="58" spans="18:78">
-      <c r="R58" s="6"/>
-      <c r="AC58" s="6"/>
-      <c r="AT58" s="6"/>
-      <c r="BI58" s="6"/>
-      <c r="BJ58" s="5"/>
-      <c r="BK58" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="59" spans="18:78">
-      <c r="R59" s="6"/>
-      <c r="AC59" s="6"/>
-      <c r="AT59" s="6"/>
-      <c r="BI59" s="6"/>
-      <c r="BJ59" s="5"/>
-      <c r="BK59" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="BT59" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="BU59" s="34"/>
-      <c r="BV59" s="34"/>
-      <c r="BW59" s="34"/>
-      <c r="BX59" s="34"/>
-      <c r="BY59" s="34"/>
-      <c r="BZ59" s="35"/>
-    </row>
-    <row r="60" spans="18:78">
-      <c r="R60" s="6"/>
-      <c r="AC60" s="6"/>
-      <c r="AT60" s="6"/>
-      <c r="BI60" s="6"/>
-      <c r="BJ60" s="7"/>
-      <c r="BK60" s="9"/>
-    </row>
-    <row r="61" spans="18:78">
-      <c r="R61" s="6"/>
-      <c r="AC61" s="6"/>
-      <c r="AT61" s="6"/>
-      <c r="BI61" s="6"/>
-    </row>
-    <row r="62" spans="18:78">
-      <c r="R62" s="6"/>
-      <c r="AC62" s="6"/>
-      <c r="AT62" s="6"/>
-      <c r="BI62" s="6"/>
-    </row>
-    <row r="63" spans="18:78">
-      <c r="R63" s="6"/>
-      <c r="AC63" s="6"/>
-      <c r="AT63" s="6"/>
-      <c r="BI63" s="6"/>
-    </row>
-    <row r="64" spans="18:78">
-      <c r="R64" s="6"/>
-      <c r="AC64" s="6"/>
-      <c r="AT64" s="6"/>
-      <c r="BI64" s="6"/>
+      <c r="BU90" s="99"/>
+      <c r="BV90" s="99"/>
+      <c r="BW90" s="99"/>
+      <c r="BX90" s="99"/>
+      <c r="BY90" s="99"/>
+      <c r="BZ90" s="100"/>
+    </row>
+    <row r="91" spans="18:78">
+      <c r="R91" s="110"/>
+      <c r="AC91" s="110"/>
+      <c r="AT91" s="110"/>
+      <c r="BI91" s="110"/>
+      <c r="BJ91" s="117"/>
+      <c r="BK91" s="118"/>
+    </row>
+    <row r="92" spans="18:78">
+      <c r="R92" s="110"/>
+      <c r="AC92" s="110"/>
+      <c r="AT92" s="110"/>
+      <c r="BI92" s="110"/>
+    </row>
+    <row r="93" spans="18:78">
+      <c r="R93" s="110"/>
+      <c r="AC93" s="110"/>
+      <c r="AT93" s="110"/>
+      <c r="BI93" s="110"/>
+    </row>
+    <row r="94" spans="18:78">
+      <c r="R94" s="110"/>
+      <c r="AC94" s="110"/>
+      <c r="AT94" s="110"/>
+      <c r="BI94" s="110"/>
+    </row>
+    <row r="95" spans="18:78">
+      <c r="R95" s="110"/>
+      <c r="AC95" s="110"/>
+      <c r="AT95" s="110"/>
+      <c r="BI95" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="N36:W36"/>
-    <mergeCell ref="Z36:AG36"/>
-    <mergeCell ref="AO36:BA36"/>
-    <mergeCell ref="BG36:BL36"/>
+    <mergeCell ref="N67:W67"/>
+    <mergeCell ref="Z67:AG67"/>
+    <mergeCell ref="AO67:BA67"/>
+    <mergeCell ref="BG67:BL67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7310,161 +8025,161 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CJ81"/>
-  <sheetFormatPr defaultColWidth="3.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:83" ht="15.75" thickBot="1"/>
-    <row r="2" spans="1:83" ht="15.75" thickBot="1">
-      <c r="B2" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31"/>
+    <row r="1" spans="1:83" ht="15" thickBot="1"/>
+    <row r="2" spans="1:83" ht="15" thickBot="1">
+      <c r="B2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:83">
       <c r="C3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:83">
       <c r="C4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:83">
       <c r="C5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:83">
       <c r="C6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:83">
-      <c r="D8" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-      <c r="X8" s="34"/>
-      <c r="Y8" s="34"/>
-      <c r="Z8" s="34"/>
-      <c r="AA8" s="34"/>
-      <c r="AB8" s="34"/>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="34"/>
-      <c r="AH8" s="34"/>
-      <c r="AI8" s="34"/>
-      <c r="AJ8" s="34"/>
-      <c r="AK8" s="34"/>
-      <c r="AL8" s="34"/>
-      <c r="AM8" s="34"/>
-      <c r="AN8" s="34"/>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="34"/>
-      <c r="AQ8" s="34"/>
-      <c r="AR8" s="34"/>
-      <c r="AS8" s="34"/>
-      <c r="AT8" s="34"/>
-      <c r="AU8" s="34"/>
-      <c r="AV8" s="34"/>
-      <c r="AW8" s="34"/>
-      <c r="AX8" s="34"/>
-      <c r="AY8" s="34"/>
-      <c r="AZ8" s="35"/>
-    </row>
-    <row r="9" spans="1:83" ht="15.75" thickBot="1"/>
-    <row r="10" spans="1:83" s="27" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A10" s="26"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:83" ht="15">
+      <c r="D8" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="31"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="31"/>
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="31"/>
+      <c r="AK8" s="31"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="31"/>
+      <c r="AO8" s="31"/>
+      <c r="AP8" s="31"/>
+      <c r="AQ8" s="31"/>
+      <c r="AR8" s="31"/>
+      <c r="AS8" s="31"/>
+      <c r="AT8" s="31"/>
+      <c r="AU8" s="31"/>
+      <c r="AV8" s="31"/>
+      <c r="AW8" s="31"/>
+      <c r="AX8" s="31"/>
+      <c r="AY8" s="31"/>
+      <c r="AZ8" s="32"/>
+    </row>
+    <row r="9" spans="1:83" ht="15" thickBot="1"/>
+    <row r="10" spans="1:83" s="26" customFormat="1" ht="15" thickBot="1">
+      <c r="A10" s="25"/>
     </row>
     <row r="13" spans="1:83">
-      <c r="K13" s="88" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="89"/>
-      <c r="M13" s="89"/>
-      <c r="N13" s="89"/>
-      <c r="O13" s="89"/>
-      <c r="P13" s="89"/>
-      <c r="Q13" s="89"/>
-      <c r="R13" s="89"/>
-      <c r="S13" s="89"/>
-      <c r="T13" s="90"/>
-      <c r="W13" s="88" t="s">
-        <v>39</v>
-      </c>
-      <c r="X13" s="89"/>
-      <c r="Y13" s="89"/>
-      <c r="Z13" s="89"/>
-      <c r="AA13" s="89"/>
-      <c r="AB13" s="89"/>
-      <c r="AC13" s="89"/>
-      <c r="AD13" s="90"/>
+      <c r="K13" s="85" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="86"/>
+      <c r="M13" s="86"/>
+      <c r="N13" s="86"/>
+      <c r="O13" s="86"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="86"/>
+      <c r="R13" s="86"/>
+      <c r="S13" s="86"/>
+      <c r="T13" s="87"/>
+      <c r="W13" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="X13" s="86"/>
+      <c r="Y13" s="86"/>
+      <c r="Z13" s="86"/>
+      <c r="AA13" s="86"/>
+      <c r="AB13" s="86"/>
+      <c r="AC13" s="86"/>
+      <c r="AD13" s="87"/>
       <c r="AJ13" s="6"/>
-      <c r="AK13" s="88" t="s">
+      <c r="AK13" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL13" s="86"/>
+      <c r="AM13" s="86"/>
+      <c r="AN13" s="86"/>
+      <c r="AO13" s="86"/>
+      <c r="AP13" s="87"/>
+      <c r="AW13" s="85" t="s">
+        <v>56</v>
+      </c>
+      <c r="AX13" s="86"/>
+      <c r="AY13" s="86"/>
+      <c r="AZ13" s="86"/>
+      <c r="BA13" s="86"/>
+      <c r="BB13" s="87"/>
+      <c r="BH13" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="AL13" s="89"/>
-      <c r="AM13" s="89"/>
-      <c r="AN13" s="89"/>
-      <c r="AO13" s="89"/>
-      <c r="AP13" s="90"/>
-      <c r="AW13" s="88" t="s">
-        <v>64</v>
-      </c>
-      <c r="AX13" s="89"/>
-      <c r="AY13" s="89"/>
-      <c r="AZ13" s="89"/>
-      <c r="BA13" s="89"/>
-      <c r="BB13" s="90"/>
-      <c r="BH13" s="88" t="s">
+      <c r="BI13" s="86"/>
+      <c r="BJ13" s="86"/>
+      <c r="BK13" s="86"/>
+      <c r="BL13" s="86"/>
+      <c r="BM13" s="87"/>
+      <c r="BR13" s="85" t="s">
+        <v>65</v>
+      </c>
+      <c r="BS13" s="86"/>
+      <c r="BT13" s="86"/>
+      <c r="BU13" s="86"/>
+      <c r="BV13" s="86"/>
+      <c r="BW13" s="87"/>
+      <c r="BZ13" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="BI13" s="89"/>
-      <c r="BJ13" s="89"/>
-      <c r="BK13" s="89"/>
-      <c r="BL13" s="89"/>
-      <c r="BM13" s="90"/>
-      <c r="BR13" s="88" t="s">
-        <v>73</v>
-      </c>
-      <c r="BS13" s="89"/>
-      <c r="BT13" s="89"/>
-      <c r="BU13" s="89"/>
-      <c r="BV13" s="89"/>
-      <c r="BW13" s="90"/>
-      <c r="BZ13" s="88" t="s">
-        <v>75</v>
-      </c>
-      <c r="CA13" s="89"/>
-      <c r="CB13" s="89"/>
-      <c r="CC13" s="89"/>
-      <c r="CD13" s="89"/>
-      <c r="CE13" s="90"/>
+      <c r="CA13" s="86"/>
+      <c r="CB13" s="86"/>
+      <c r="CC13" s="86"/>
+      <c r="CD13" s="86"/>
+      <c r="CE13" s="87"/>
     </row>
     <row r="14" spans="1:83">
       <c r="O14" s="6"/>
@@ -7476,17 +8191,17 @@
       <c r="CB14" s="4"/>
     </row>
     <row r="15" spans="1:83">
-      <c r="B15" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
+      <c r="B15" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="32"/>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="O15" s="6"/>
       <c r="Z15" s="6"/>
@@ -7498,11 +8213,11 @@
     </row>
     <row r="16" spans="1:83">
       <c r="I16" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="O16" s="6"/>
       <c r="P16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="Z16" s="6"/>
       <c r="AM16" s="6"/>
@@ -7514,7 +8229,7 @@
     <row r="17" spans="15:80">
       <c r="O17" s="6"/>
       <c r="P17" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Z17" s="6"/>
       <c r="AM17" s="6"/>
@@ -7526,7 +8241,7 @@
     <row r="18" spans="15:80">
       <c r="O18" s="6"/>
       <c r="P18" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Z18" s="6"/>
       <c r="AM18" s="6"/>
@@ -7538,11 +8253,11 @@
     <row r="19" spans="15:80">
       <c r="O19" s="6"/>
       <c r="Q19" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="Z19" s="6"/>
       <c r="AA19" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM19" s="6"/>
       <c r="AY19" s="6"/>
@@ -7577,7 +8292,7 @@
       <c r="O22" s="6"/>
       <c r="Z22" s="6"/>
       <c r="AB22" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="AM22" s="6"/>
       <c r="AY22" s="6"/>
@@ -7589,7 +8304,7 @@
       <c r="O23" s="6"/>
       <c r="Z23" s="6"/>
       <c r="AB23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM23" s="6"/>
       <c r="AY23" s="6"/>
@@ -7601,11 +8316,11 @@
       <c r="O24" s="6"/>
       <c r="Z24" s="6"/>
       <c r="AB24" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="AM24" s="6"/>
       <c r="AN24" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="AY24" s="6"/>
       <c r="BJ24" s="6"/>
@@ -7642,11 +8357,11 @@
       <c r="O27" s="6"/>
       <c r="Z27" s="6"/>
       <c r="AB27" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM27" s="6"/>
       <c r="AN27" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="AO27" s="6"/>
       <c r="AY27" s="6"/>
@@ -7659,8 +8374,8 @@
       <c r="Z28" s="6"/>
       <c r="AB28" s="6"/>
       <c r="AM28" s="6"/>
-      <c r="AO28" s="37" t="s">
-        <v>62</v>
+      <c r="AO28" s="34" t="s">
+        <v>54</v>
       </c>
       <c r="AY28" s="6"/>
       <c r="BJ28" s="6"/>
@@ -7685,7 +8400,7 @@
       <c r="AM30" s="6"/>
       <c r="AO30" s="6"/>
       <c r="AP30" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="AY30" s="6"/>
       <c r="BJ30" s="6"/>
@@ -7699,7 +8414,7 @@
       <c r="AM31" s="6"/>
       <c r="AO31" s="6"/>
       <c r="AP31" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AY31" s="6"/>
       <c r="BJ31" s="6"/>
@@ -7737,11 +8452,11 @@
       <c r="O34" s="6"/>
       <c r="Z34" s="6"/>
       <c r="AB34" s="6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="AM34" s="6"/>
       <c r="AW34" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="AY34" s="6"/>
       <c r="BJ34" s="6"/>
@@ -7780,10 +8495,10 @@
       <c r="AY37" s="6"/>
       <c r="AZ37" s="5"/>
       <c r="BA37" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="BJ37" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="BT37" s="6"/>
       <c r="CB37" s="6"/>
@@ -7797,7 +8512,7 @@
       <c r="BA38" s="6"/>
       <c r="BJ38" s="6"/>
       <c r="BK38" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="BM38" s="8"/>
       <c r="BN38" s="8"/>
@@ -7840,7 +8555,7 @@
       <c r="BA41" s="6"/>
       <c r="BJ41" s="6"/>
       <c r="BL41" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="BT41" s="6"/>
       <c r="CB41" s="6"/>
@@ -7853,8 +8568,8 @@
       <c r="AZ42" s="5"/>
       <c r="BA42" s="6"/>
       <c r="BJ42" s="6"/>
-      <c r="BL42" s="37" t="s">
-        <v>138</v>
+      <c r="BL42" s="34" t="s">
+        <v>130</v>
       </c>
       <c r="BT42" s="6"/>
       <c r="CB42" s="6"/>
@@ -7910,1017 +8625,1017 @@
       <c r="BT46" s="6"/>
       <c r="CB46" s="6"/>
     </row>
-    <row r="47" spans="15:88">
+    <row r="47" spans="15:88" ht="15">
       <c r="O47" s="6"/>
       <c r="Z47" s="6"/>
       <c r="AM47" s="6"/>
       <c r="AW47" s="6"/>
-      <c r="AX47" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="AY47" s="39"/>
-      <c r="AZ47" s="40"/>
-      <c r="BA47" s="39"/>
-      <c r="BB47" s="41"/>
-      <c r="BC47" s="41"/>
-      <c r="BD47" s="41"/>
-      <c r="BE47" s="41"/>
-      <c r="BF47" s="41"/>
-      <c r="BG47" s="41"/>
-      <c r="BH47" s="41"/>
-      <c r="BI47" s="41"/>
-      <c r="BJ47" s="39"/>
-      <c r="BK47" s="41"/>
-      <c r="BL47" s="41"/>
-      <c r="BM47" s="41"/>
-      <c r="BN47" s="41"/>
-      <c r="BO47" s="41"/>
-      <c r="BP47" s="41"/>
-      <c r="BQ47" s="41"/>
-      <c r="BR47" s="41"/>
-      <c r="BS47" s="41"/>
-      <c r="BT47" s="39"/>
-      <c r="BU47" s="41"/>
-      <c r="BV47" s="41"/>
-      <c r="BW47" s="41"/>
-      <c r="BX47" s="41"/>
-      <c r="BY47" s="41"/>
-      <c r="BZ47" s="41"/>
-      <c r="CA47" s="41"/>
-      <c r="CB47" s="39"/>
-      <c r="CC47" s="41"/>
-      <c r="CD47" s="41"/>
-      <c r="CE47" s="41"/>
-      <c r="CF47" s="41"/>
-      <c r="CG47" s="41"/>
-      <c r="CH47" s="41"/>
-      <c r="CI47" s="41"/>
-      <c r="CJ47" s="39"/>
+      <c r="AX47" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="AY47" s="36"/>
+      <c r="AZ47" s="37"/>
+      <c r="BA47" s="36"/>
+      <c r="BB47" s="38"/>
+      <c r="BC47" s="38"/>
+      <c r="BD47" s="38"/>
+      <c r="BE47" s="38"/>
+      <c r="BF47" s="38"/>
+      <c r="BG47" s="38"/>
+      <c r="BH47" s="38"/>
+      <c r="BI47" s="38"/>
+      <c r="BJ47" s="36"/>
+      <c r="BK47" s="38"/>
+      <c r="BL47" s="38"/>
+      <c r="BM47" s="38"/>
+      <c r="BN47" s="38"/>
+      <c r="BO47" s="38"/>
+      <c r="BP47" s="38"/>
+      <c r="BQ47" s="38"/>
+      <c r="BR47" s="38"/>
+      <c r="BS47" s="38"/>
+      <c r="BT47" s="36"/>
+      <c r="BU47" s="38"/>
+      <c r="BV47" s="38"/>
+      <c r="BW47" s="38"/>
+      <c r="BX47" s="38"/>
+      <c r="BY47" s="38"/>
+      <c r="BZ47" s="38"/>
+      <c r="CA47" s="38"/>
+      <c r="CB47" s="36"/>
+      <c r="CC47" s="38"/>
+      <c r="CD47" s="38"/>
+      <c r="CE47" s="38"/>
+      <c r="CF47" s="38"/>
+      <c r="CG47" s="38"/>
+      <c r="CH47" s="38"/>
+      <c r="CI47" s="38"/>
+      <c r="CJ47" s="36"/>
     </row>
     <row r="48" spans="15:88">
       <c r="O48" s="6"/>
       <c r="Z48" s="6"/>
       <c r="AM48" s="6"/>
       <c r="AW48" s="6"/>
-      <c r="AX48" s="42"/>
-      <c r="AY48" s="43"/>
-      <c r="AZ48" s="44"/>
-      <c r="BA48" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="BB48" s="45"/>
-      <c r="BC48" s="45"/>
-      <c r="BD48" s="42"/>
-      <c r="BE48" s="45"/>
-      <c r="BF48" s="42"/>
-      <c r="BG48" s="42"/>
-      <c r="BH48" s="42"/>
-      <c r="BI48" s="42"/>
-      <c r="BJ48" s="43"/>
-      <c r="BK48" s="42"/>
-      <c r="BL48" s="42"/>
-      <c r="BM48" s="42"/>
-      <c r="BN48" s="42"/>
-      <c r="BO48" s="42"/>
-      <c r="BP48" s="42"/>
-      <c r="BQ48" s="42"/>
-      <c r="BR48" s="42"/>
-      <c r="BS48" s="42"/>
-      <c r="BT48" s="43"/>
-      <c r="BU48" s="42"/>
-      <c r="BV48" s="42"/>
-      <c r="BW48" s="42"/>
-      <c r="BX48" s="42"/>
-      <c r="BY48" s="42"/>
-      <c r="BZ48" s="42"/>
-      <c r="CA48" s="42"/>
-      <c r="CB48" s="43"/>
-      <c r="CC48" s="42"/>
-      <c r="CD48" s="42"/>
-      <c r="CE48" s="42"/>
-      <c r="CF48" s="42"/>
-      <c r="CG48" s="42"/>
-      <c r="CH48" s="42"/>
-      <c r="CI48" s="42"/>
-      <c r="CJ48" s="43"/>
+      <c r="AX48" s="39"/>
+      <c r="AY48" s="40"/>
+      <c r="AZ48" s="41"/>
+      <c r="BA48" s="40" t="s">
+        <v>63</v>
+      </c>
+      <c r="BB48" s="42"/>
+      <c r="BC48" s="42"/>
+      <c r="BD48" s="39"/>
+      <c r="BE48" s="42"/>
+      <c r="BF48" s="39"/>
+      <c r="BG48" s="39"/>
+      <c r="BH48" s="39"/>
+      <c r="BI48" s="39"/>
+      <c r="BJ48" s="40"/>
+      <c r="BK48" s="39"/>
+      <c r="BL48" s="39"/>
+      <c r="BM48" s="39"/>
+      <c r="BN48" s="39"/>
+      <c r="BO48" s="39"/>
+      <c r="BP48" s="39"/>
+      <c r="BQ48" s="39"/>
+      <c r="BR48" s="39"/>
+      <c r="BS48" s="39"/>
+      <c r="BT48" s="40"/>
+      <c r="BU48" s="39"/>
+      <c r="BV48" s="39"/>
+      <c r="BW48" s="39"/>
+      <c r="BX48" s="39"/>
+      <c r="BY48" s="39"/>
+      <c r="BZ48" s="39"/>
+      <c r="CA48" s="39"/>
+      <c r="CB48" s="40"/>
+      <c r="CC48" s="39"/>
+      <c r="CD48" s="39"/>
+      <c r="CE48" s="39"/>
+      <c r="CF48" s="39"/>
+      <c r="CG48" s="39"/>
+      <c r="CH48" s="39"/>
+      <c r="CI48" s="39"/>
+      <c r="CJ48" s="40"/>
     </row>
     <row r="49" spans="15:88">
       <c r="O49" s="6"/>
       <c r="Z49" s="6"/>
       <c r="AM49" s="6"/>
       <c r="AW49" s="6"/>
-      <c r="AX49" s="42"/>
-      <c r="AY49" s="43"/>
-      <c r="AZ49" s="44"/>
-      <c r="BA49" s="43"/>
-      <c r="BB49" s="46"/>
-      <c r="BC49" s="47"/>
-      <c r="BD49" s="47"/>
-      <c r="BE49" s="48"/>
-      <c r="BF49" s="42"/>
-      <c r="BG49" s="42"/>
-      <c r="BH49" s="42"/>
-      <c r="BI49" s="42"/>
-      <c r="BJ49" s="43"/>
-      <c r="BK49" s="42"/>
-      <c r="BL49" s="42"/>
-      <c r="BM49" s="42"/>
-      <c r="BN49" s="42"/>
-      <c r="BO49" s="42"/>
-      <c r="BP49" s="42"/>
-      <c r="BQ49" s="42"/>
-      <c r="BR49" s="42"/>
-      <c r="BS49" s="42"/>
-      <c r="BT49" s="43"/>
-      <c r="BU49" s="42"/>
-      <c r="BV49" s="42"/>
-      <c r="BW49" s="42"/>
-      <c r="BX49" s="42"/>
-      <c r="BY49" s="42"/>
-      <c r="BZ49" s="42"/>
-      <c r="CA49" s="42"/>
-      <c r="CB49" s="43"/>
-      <c r="CC49" s="42"/>
-      <c r="CD49" s="42"/>
-      <c r="CE49" s="42"/>
-      <c r="CF49" s="42"/>
-      <c r="CG49" s="42"/>
-      <c r="CH49" s="42"/>
-      <c r="CI49" s="42"/>
-      <c r="CJ49" s="43"/>
+      <c r="AX49" s="39"/>
+      <c r="AY49" s="40"/>
+      <c r="AZ49" s="41"/>
+      <c r="BA49" s="40"/>
+      <c r="BB49" s="43"/>
+      <c r="BC49" s="44"/>
+      <c r="BD49" s="44"/>
+      <c r="BE49" s="45"/>
+      <c r="BF49" s="39"/>
+      <c r="BG49" s="39"/>
+      <c r="BH49" s="39"/>
+      <c r="BI49" s="39"/>
+      <c r="BJ49" s="40"/>
+      <c r="BK49" s="39"/>
+      <c r="BL49" s="39"/>
+      <c r="BM49" s="39"/>
+      <c r="BN49" s="39"/>
+      <c r="BO49" s="39"/>
+      <c r="BP49" s="39"/>
+      <c r="BQ49" s="39"/>
+      <c r="BR49" s="39"/>
+      <c r="BS49" s="39"/>
+      <c r="BT49" s="40"/>
+      <c r="BU49" s="39"/>
+      <c r="BV49" s="39"/>
+      <c r="BW49" s="39"/>
+      <c r="BX49" s="39"/>
+      <c r="BY49" s="39"/>
+      <c r="BZ49" s="39"/>
+      <c r="CA49" s="39"/>
+      <c r="CB49" s="40"/>
+      <c r="CC49" s="39"/>
+      <c r="CD49" s="39"/>
+      <c r="CE49" s="39"/>
+      <c r="CF49" s="39"/>
+      <c r="CG49" s="39"/>
+      <c r="CH49" s="39"/>
+      <c r="CI49" s="39"/>
+      <c r="CJ49" s="40"/>
     </row>
     <row r="50" spans="15:88">
       <c r="O50" s="6"/>
       <c r="Z50" s="6"/>
       <c r="AM50" s="6"/>
       <c r="AW50" s="6"/>
-      <c r="AX50" s="42"/>
-      <c r="AY50" s="43"/>
-      <c r="AZ50" s="44"/>
-      <c r="BA50" s="43"/>
-      <c r="BB50" s="40"/>
-      <c r="BC50" s="39"/>
-      <c r="BD50" s="42"/>
-      <c r="BE50" s="42"/>
-      <c r="BF50" s="42"/>
-      <c r="BG50" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="BH50" s="42"/>
-      <c r="BI50" s="42"/>
-      <c r="BJ50" s="43"/>
-      <c r="BK50" s="42"/>
-      <c r="BL50" s="42"/>
-      <c r="BM50" s="42"/>
-      <c r="BN50" s="42"/>
-      <c r="BO50" s="42"/>
-      <c r="BP50" s="42"/>
-      <c r="BQ50" s="42"/>
-      <c r="BR50" s="42"/>
-      <c r="BS50" s="42"/>
-      <c r="BT50" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="BU50" s="42"/>
-      <c r="BV50" s="42"/>
-      <c r="BW50" s="42"/>
-      <c r="BX50" s="42"/>
-      <c r="BY50" s="42"/>
-      <c r="BZ50" s="42"/>
-      <c r="CA50" s="42"/>
-      <c r="CB50" s="43"/>
-      <c r="CC50" s="42"/>
-      <c r="CD50" s="42"/>
-      <c r="CE50" s="42"/>
-      <c r="CF50" s="42"/>
-      <c r="CG50" s="42"/>
-      <c r="CH50" s="42"/>
-      <c r="CI50" s="42"/>
-      <c r="CJ50" s="43"/>
+      <c r="AX50" s="39"/>
+      <c r="AY50" s="40"/>
+      <c r="AZ50" s="41"/>
+      <c r="BA50" s="40"/>
+      <c r="BB50" s="37"/>
+      <c r="BC50" s="36"/>
+      <c r="BD50" s="39"/>
+      <c r="BE50" s="39"/>
+      <c r="BF50" s="39"/>
+      <c r="BG50" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="BH50" s="39"/>
+      <c r="BI50" s="39"/>
+      <c r="BJ50" s="40"/>
+      <c r="BK50" s="39"/>
+      <c r="BL50" s="39"/>
+      <c r="BM50" s="39"/>
+      <c r="BN50" s="39"/>
+      <c r="BO50" s="39"/>
+      <c r="BP50" s="39"/>
+      <c r="BQ50" s="39"/>
+      <c r="BR50" s="39"/>
+      <c r="BS50" s="39"/>
+      <c r="BT50" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="BU50" s="39"/>
+      <c r="BV50" s="39"/>
+      <c r="BW50" s="39"/>
+      <c r="BX50" s="39"/>
+      <c r="BY50" s="39"/>
+      <c r="BZ50" s="39"/>
+      <c r="CA50" s="39"/>
+      <c r="CB50" s="40"/>
+      <c r="CC50" s="39"/>
+      <c r="CD50" s="39"/>
+      <c r="CE50" s="39"/>
+      <c r="CF50" s="39"/>
+      <c r="CG50" s="39"/>
+      <c r="CH50" s="39"/>
+      <c r="CI50" s="39"/>
+      <c r="CJ50" s="40"/>
     </row>
     <row r="51" spans="15:88">
       <c r="O51" s="6"/>
       <c r="Z51" s="6"/>
       <c r="AM51" s="6"/>
       <c r="AW51" s="6"/>
-      <c r="AX51" s="42"/>
-      <c r="AY51" s="43"/>
-      <c r="AZ51" s="44"/>
-      <c r="BA51" s="43"/>
-      <c r="BB51" s="44"/>
-      <c r="BC51" s="43"/>
-      <c r="BD51" s="42"/>
-      <c r="BE51" s="42"/>
-      <c r="BF51" s="42"/>
-      <c r="BG51" s="42"/>
-      <c r="BH51" s="42"/>
-      <c r="BI51" s="42"/>
-      <c r="BJ51" s="43"/>
-      <c r="BK51" s="42"/>
-      <c r="BL51" s="42"/>
-      <c r="BM51" s="42"/>
-      <c r="BN51" s="42"/>
-      <c r="BO51" s="42"/>
-      <c r="BP51" s="42"/>
-      <c r="BQ51" s="42"/>
-      <c r="BR51" s="42"/>
-      <c r="BS51" s="42"/>
-      <c r="BT51" s="43"/>
-      <c r="BU51" s="46"/>
-      <c r="BV51" s="47"/>
-      <c r="BW51" s="47"/>
-      <c r="BX51" s="48"/>
-      <c r="BY51" s="42"/>
-      <c r="BZ51" s="42"/>
-      <c r="CA51" s="42"/>
-      <c r="CB51" s="43"/>
-      <c r="CC51" s="42"/>
-      <c r="CD51" s="42"/>
-      <c r="CE51" s="42"/>
-      <c r="CF51" s="42"/>
-      <c r="CG51" s="42"/>
-      <c r="CH51" s="42"/>
-      <c r="CI51" s="42"/>
-      <c r="CJ51" s="43"/>
+      <c r="AX51" s="39"/>
+      <c r="AY51" s="40"/>
+      <c r="AZ51" s="41"/>
+      <c r="BA51" s="40"/>
+      <c r="BB51" s="41"/>
+      <c r="BC51" s="40"/>
+      <c r="BD51" s="39"/>
+      <c r="BE51" s="39"/>
+      <c r="BF51" s="39"/>
+      <c r="BG51" s="39"/>
+      <c r="BH51" s="39"/>
+      <c r="BI51" s="39"/>
+      <c r="BJ51" s="40"/>
+      <c r="BK51" s="39"/>
+      <c r="BL51" s="39"/>
+      <c r="BM51" s="39"/>
+      <c r="BN51" s="39"/>
+      <c r="BO51" s="39"/>
+      <c r="BP51" s="39"/>
+      <c r="BQ51" s="39"/>
+      <c r="BR51" s="39"/>
+      <c r="BS51" s="39"/>
+      <c r="BT51" s="40"/>
+      <c r="BU51" s="43"/>
+      <c r="BV51" s="44"/>
+      <c r="BW51" s="44"/>
+      <c r="BX51" s="45"/>
+      <c r="BY51" s="39"/>
+      <c r="BZ51" s="39"/>
+      <c r="CA51" s="39"/>
+      <c r="CB51" s="40"/>
+      <c r="CC51" s="39"/>
+      <c r="CD51" s="39"/>
+      <c r="CE51" s="39"/>
+      <c r="CF51" s="39"/>
+      <c r="CG51" s="39"/>
+      <c r="CH51" s="39"/>
+      <c r="CI51" s="39"/>
+      <c r="CJ51" s="40"/>
     </row>
     <row r="52" spans="15:88">
       <c r="O52" s="6"/>
       <c r="Z52" s="6"/>
       <c r="AM52" s="6"/>
       <c r="AW52" s="6"/>
-      <c r="AX52" s="42"/>
-      <c r="AY52" s="43"/>
-      <c r="AZ52" s="44"/>
-      <c r="BA52" s="42"/>
-      <c r="BB52" s="44"/>
-      <c r="BC52" s="43"/>
-      <c r="BD52" s="42"/>
-      <c r="BE52" s="42"/>
-      <c r="BF52" s="42"/>
-      <c r="BG52" s="42"/>
-      <c r="BH52" s="42"/>
-      <c r="BI52" s="42"/>
-      <c r="BJ52" s="43"/>
-      <c r="BK52" s="42"/>
-      <c r="BL52" s="42"/>
-      <c r="BM52" s="42"/>
-      <c r="BN52" s="42"/>
-      <c r="BO52" s="42"/>
-      <c r="BP52" s="42"/>
-      <c r="BQ52" s="42"/>
-      <c r="BR52" s="42"/>
-      <c r="BS52" s="42"/>
-      <c r="BT52" s="43"/>
-      <c r="BU52" s="40"/>
-      <c r="BV52" s="39"/>
-      <c r="BW52" s="42"/>
-      <c r="BX52" s="42"/>
-      <c r="BY52" s="42"/>
-      <c r="BZ52" s="42"/>
-      <c r="CA52" s="42"/>
-      <c r="CB52" s="43"/>
-      <c r="CC52" s="42"/>
-      <c r="CD52" s="42"/>
-      <c r="CE52" s="42"/>
-      <c r="CF52" s="42"/>
-      <c r="CG52" s="42"/>
-      <c r="CH52" s="42"/>
-      <c r="CI52" s="42"/>
-      <c r="CJ52" s="43"/>
+      <c r="AX52" s="39"/>
+      <c r="AY52" s="40"/>
+      <c r="AZ52" s="41"/>
+      <c r="BA52" s="39"/>
+      <c r="BB52" s="41"/>
+      <c r="BC52" s="40"/>
+      <c r="BD52" s="39"/>
+      <c r="BE52" s="39"/>
+      <c r="BF52" s="39"/>
+      <c r="BG52" s="39"/>
+      <c r="BH52" s="39"/>
+      <c r="BI52" s="39"/>
+      <c r="BJ52" s="40"/>
+      <c r="BK52" s="39"/>
+      <c r="BL52" s="39"/>
+      <c r="BM52" s="39"/>
+      <c r="BN52" s="39"/>
+      <c r="BO52" s="39"/>
+      <c r="BP52" s="39"/>
+      <c r="BQ52" s="39"/>
+      <c r="BR52" s="39"/>
+      <c r="BS52" s="39"/>
+      <c r="BT52" s="40"/>
+      <c r="BU52" s="37"/>
+      <c r="BV52" s="36"/>
+      <c r="BW52" s="39"/>
+      <c r="BX52" s="39"/>
+      <c r="BY52" s="39"/>
+      <c r="BZ52" s="39"/>
+      <c r="CA52" s="39"/>
+      <c r="CB52" s="40"/>
+      <c r="CC52" s="39"/>
+      <c r="CD52" s="39"/>
+      <c r="CE52" s="39"/>
+      <c r="CF52" s="39"/>
+      <c r="CG52" s="39"/>
+      <c r="CH52" s="39"/>
+      <c r="CI52" s="39"/>
+      <c r="CJ52" s="40"/>
     </row>
     <row r="53" spans="15:88">
       <c r="O53" s="6"/>
       <c r="Z53" s="6"/>
       <c r="AM53" s="6"/>
       <c r="AW53" s="6"/>
-      <c r="AX53" s="42"/>
-      <c r="AY53" s="43"/>
-      <c r="AZ53" s="44"/>
-      <c r="BA53" s="42"/>
-      <c r="BB53" s="44"/>
-      <c r="BC53" s="43"/>
-      <c r="BD53" s="42"/>
-      <c r="BE53" s="42"/>
-      <c r="BF53" s="42"/>
-      <c r="BG53" s="42"/>
-      <c r="BH53" s="42"/>
-      <c r="BI53" s="42"/>
-      <c r="BJ53" s="43"/>
-      <c r="BK53" s="42"/>
-      <c r="BL53" s="42"/>
-      <c r="BM53" s="42"/>
-      <c r="BN53" s="42"/>
-      <c r="BO53" s="42"/>
-      <c r="BP53" s="42"/>
-      <c r="BQ53" s="42"/>
-      <c r="BR53" s="42"/>
-      <c r="BS53" s="42"/>
-      <c r="BT53" s="43"/>
-      <c r="BU53" s="44"/>
-      <c r="BV53" s="43" t="s">
-        <v>97</v>
-      </c>
-      <c r="BW53" s="42"/>
-      <c r="BX53" s="42"/>
-      <c r="BY53" s="42"/>
-      <c r="BZ53" s="42"/>
-      <c r="CA53" s="42"/>
-      <c r="CB53" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="CC53" s="42"/>
-      <c r="CD53" s="42"/>
-      <c r="CE53" s="42"/>
-      <c r="CF53" s="42"/>
-      <c r="CG53" s="42"/>
-      <c r="CH53" s="42"/>
-      <c r="CI53" s="42"/>
-      <c r="CJ53" s="43"/>
+      <c r="AX53" s="39"/>
+      <c r="AY53" s="40"/>
+      <c r="AZ53" s="41"/>
+      <c r="BA53" s="39"/>
+      <c r="BB53" s="41"/>
+      <c r="BC53" s="40"/>
+      <c r="BD53" s="39"/>
+      <c r="BE53" s="39"/>
+      <c r="BF53" s="39"/>
+      <c r="BG53" s="39"/>
+      <c r="BH53" s="39"/>
+      <c r="BI53" s="39"/>
+      <c r="BJ53" s="40"/>
+      <c r="BK53" s="39"/>
+      <c r="BL53" s="39"/>
+      <c r="BM53" s="39"/>
+      <c r="BN53" s="39"/>
+      <c r="BO53" s="39"/>
+      <c r="BP53" s="39"/>
+      <c r="BQ53" s="39"/>
+      <c r="BR53" s="39"/>
+      <c r="BS53" s="39"/>
+      <c r="BT53" s="40"/>
+      <c r="BU53" s="41"/>
+      <c r="BV53" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="BW53" s="39"/>
+      <c r="BX53" s="39"/>
+      <c r="BY53" s="39"/>
+      <c r="BZ53" s="39"/>
+      <c r="CA53" s="39"/>
+      <c r="CB53" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="CC53" s="39"/>
+      <c r="CD53" s="39"/>
+      <c r="CE53" s="39"/>
+      <c r="CF53" s="39"/>
+      <c r="CG53" s="39"/>
+      <c r="CH53" s="39"/>
+      <c r="CI53" s="39"/>
+      <c r="CJ53" s="40"/>
     </row>
     <row r="54" spans="15:88">
       <c r="O54" s="6"/>
       <c r="Z54" s="6"/>
       <c r="AM54" s="6"/>
       <c r="AW54" s="6"/>
-      <c r="AX54" s="42"/>
-      <c r="AY54" s="43"/>
-      <c r="AZ54" s="44"/>
-      <c r="BA54" s="42"/>
-      <c r="BB54" s="44"/>
-      <c r="BC54" s="43"/>
-      <c r="BD54" s="42"/>
-      <c r="BE54" s="42"/>
-      <c r="BF54" s="42"/>
-      <c r="BG54" s="42"/>
-      <c r="BH54" s="42"/>
-      <c r="BI54" s="42"/>
-      <c r="BJ54" s="43"/>
-      <c r="BK54" s="42"/>
-      <c r="BL54" s="42"/>
-      <c r="BM54" s="42"/>
-      <c r="BN54" s="42"/>
-      <c r="BO54" s="42"/>
-      <c r="BP54" s="42"/>
-      <c r="BQ54" s="42"/>
-      <c r="BR54" s="42"/>
-      <c r="BS54" s="42"/>
-      <c r="BT54" s="43"/>
-      <c r="BU54" s="44"/>
-      <c r="BV54" s="43"/>
-      <c r="BW54" s="42"/>
-      <c r="BX54" s="42"/>
-      <c r="BY54" s="42"/>
-      <c r="BZ54" s="42"/>
-      <c r="CA54" s="42"/>
-      <c r="CB54" s="43"/>
-      <c r="CC54" s="46"/>
-      <c r="CD54" s="47"/>
-      <c r="CE54" s="47"/>
-      <c r="CF54" s="48"/>
-      <c r="CG54" s="42"/>
-      <c r="CH54" s="42"/>
-      <c r="CI54" s="42"/>
-      <c r="CJ54" s="43"/>
+      <c r="AX54" s="39"/>
+      <c r="AY54" s="40"/>
+      <c r="AZ54" s="41"/>
+      <c r="BA54" s="39"/>
+      <c r="BB54" s="41"/>
+      <c r="BC54" s="40"/>
+      <c r="BD54" s="39"/>
+      <c r="BE54" s="39"/>
+      <c r="BF54" s="39"/>
+      <c r="BG54" s="39"/>
+      <c r="BH54" s="39"/>
+      <c r="BI54" s="39"/>
+      <c r="BJ54" s="40"/>
+      <c r="BK54" s="39"/>
+      <c r="BL54" s="39"/>
+      <c r="BM54" s="39"/>
+      <c r="BN54" s="39"/>
+      <c r="BO54" s="39"/>
+      <c r="BP54" s="39"/>
+      <c r="BQ54" s="39"/>
+      <c r="BR54" s="39"/>
+      <c r="BS54" s="39"/>
+      <c r="BT54" s="40"/>
+      <c r="BU54" s="41"/>
+      <c r="BV54" s="40"/>
+      <c r="BW54" s="39"/>
+      <c r="BX54" s="39"/>
+      <c r="BY54" s="39"/>
+      <c r="BZ54" s="39"/>
+      <c r="CA54" s="39"/>
+      <c r="CB54" s="40"/>
+      <c r="CC54" s="43"/>
+      <c r="CD54" s="44"/>
+      <c r="CE54" s="44"/>
+      <c r="CF54" s="45"/>
+      <c r="CG54" s="39"/>
+      <c r="CH54" s="39"/>
+      <c r="CI54" s="39"/>
+      <c r="CJ54" s="40"/>
     </row>
     <row r="55" spans="15:88">
       <c r="O55" s="6"/>
       <c r="Z55" s="6"/>
       <c r="AM55" s="6"/>
       <c r="AW55" s="6"/>
-      <c r="AX55" s="42"/>
-      <c r="AY55" s="43"/>
-      <c r="AZ55" s="44"/>
-      <c r="BA55" s="42"/>
-      <c r="BB55" s="44"/>
-      <c r="BC55" s="43"/>
-      <c r="BD55" s="42"/>
-      <c r="BE55" s="42"/>
-      <c r="BF55" s="42"/>
-      <c r="BG55" s="42"/>
-      <c r="BH55" s="42"/>
-      <c r="BI55" s="42"/>
-      <c r="BJ55" s="43"/>
-      <c r="BK55" s="42"/>
-      <c r="BL55" s="42"/>
-      <c r="BM55" s="42"/>
-      <c r="BN55" s="42"/>
-      <c r="BO55" s="42"/>
-      <c r="BP55" s="42"/>
-      <c r="BQ55" s="42"/>
-      <c r="BR55" s="42"/>
-      <c r="BS55" s="42"/>
-      <c r="BT55" s="43"/>
-      <c r="BU55" s="44"/>
-      <c r="BV55" s="43"/>
-      <c r="BW55" s="42"/>
-      <c r="BX55" s="42"/>
-      <c r="BY55" s="42"/>
-      <c r="BZ55" s="42"/>
-      <c r="CA55" s="42"/>
-      <c r="CB55" s="43"/>
-      <c r="CC55" s="40"/>
-      <c r="CD55" s="39"/>
-      <c r="CE55" s="42"/>
-      <c r="CF55" s="42"/>
-      <c r="CG55" s="42"/>
-      <c r="CH55" s="42"/>
-      <c r="CI55" s="42"/>
-      <c r="CJ55" s="43"/>
+      <c r="AX55" s="39"/>
+      <c r="AY55" s="40"/>
+      <c r="AZ55" s="41"/>
+      <c r="BA55" s="39"/>
+      <c r="BB55" s="41"/>
+      <c r="BC55" s="40"/>
+      <c r="BD55" s="39"/>
+      <c r="BE55" s="39"/>
+      <c r="BF55" s="39"/>
+      <c r="BG55" s="39"/>
+      <c r="BH55" s="39"/>
+      <c r="BI55" s="39"/>
+      <c r="BJ55" s="40"/>
+      <c r="BK55" s="39"/>
+      <c r="BL55" s="39"/>
+      <c r="BM55" s="39"/>
+      <c r="BN55" s="39"/>
+      <c r="BO55" s="39"/>
+      <c r="BP55" s="39"/>
+      <c r="BQ55" s="39"/>
+      <c r="BR55" s="39"/>
+      <c r="BS55" s="39"/>
+      <c r="BT55" s="40"/>
+      <c r="BU55" s="41"/>
+      <c r="BV55" s="40"/>
+      <c r="BW55" s="39"/>
+      <c r="BX55" s="39"/>
+      <c r="BY55" s="39"/>
+      <c r="BZ55" s="39"/>
+      <c r="CA55" s="39"/>
+      <c r="CB55" s="40"/>
+      <c r="CC55" s="37"/>
+      <c r="CD55" s="36"/>
+      <c r="CE55" s="39"/>
+      <c r="CF55" s="39"/>
+      <c r="CG55" s="39"/>
+      <c r="CH55" s="39"/>
+      <c r="CI55" s="39"/>
+      <c r="CJ55" s="40"/>
     </row>
     <row r="56" spans="15:88">
       <c r="O56" s="6"/>
       <c r="Z56" s="6"/>
       <c r="AM56" s="6"/>
       <c r="AW56" s="6"/>
-      <c r="AX56" s="42"/>
-      <c r="AY56" s="43"/>
-      <c r="AZ56" s="44"/>
-      <c r="BA56" s="42"/>
-      <c r="BB56" s="44"/>
-      <c r="BC56" s="43"/>
-      <c r="BD56" s="42"/>
-      <c r="BE56" s="42"/>
-      <c r="BF56" s="42"/>
-      <c r="BG56" s="42"/>
-      <c r="BH56" s="42"/>
-      <c r="BI56" s="42"/>
-      <c r="BJ56" s="43"/>
-      <c r="BK56" s="42"/>
-      <c r="BL56" s="42"/>
-      <c r="BM56" s="42"/>
-      <c r="BN56" s="42"/>
-      <c r="BO56" s="42"/>
-      <c r="BP56" s="42"/>
-      <c r="BQ56" s="42"/>
-      <c r="BR56" s="42"/>
-      <c r="BS56" s="42"/>
-      <c r="BT56" s="43"/>
-      <c r="BU56" s="44"/>
-      <c r="BV56" s="43"/>
-      <c r="BW56" s="42"/>
-      <c r="BX56" s="42"/>
-      <c r="BY56" s="42"/>
-      <c r="BZ56" s="42"/>
-      <c r="CA56" s="42"/>
-      <c r="CB56" s="43"/>
-      <c r="CC56" s="44"/>
-      <c r="CD56" s="43"/>
-      <c r="CE56" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="CF56" s="42"/>
-      <c r="CG56" s="42"/>
-      <c r="CH56" s="42"/>
-      <c r="CI56" s="42"/>
-      <c r="CJ56" s="43"/>
+      <c r="AX56" s="39"/>
+      <c r="AY56" s="40"/>
+      <c r="AZ56" s="41"/>
+      <c r="BA56" s="39"/>
+      <c r="BB56" s="41"/>
+      <c r="BC56" s="40"/>
+      <c r="BD56" s="39"/>
+      <c r="BE56" s="39"/>
+      <c r="BF56" s="39"/>
+      <c r="BG56" s="39"/>
+      <c r="BH56" s="39"/>
+      <c r="BI56" s="39"/>
+      <c r="BJ56" s="40"/>
+      <c r="BK56" s="39"/>
+      <c r="BL56" s="39"/>
+      <c r="BM56" s="39"/>
+      <c r="BN56" s="39"/>
+      <c r="BO56" s="39"/>
+      <c r="BP56" s="39"/>
+      <c r="BQ56" s="39"/>
+      <c r="BR56" s="39"/>
+      <c r="BS56" s="39"/>
+      <c r="BT56" s="40"/>
+      <c r="BU56" s="41"/>
+      <c r="BV56" s="40"/>
+      <c r="BW56" s="39"/>
+      <c r="BX56" s="39"/>
+      <c r="BY56" s="39"/>
+      <c r="BZ56" s="39"/>
+      <c r="CA56" s="39"/>
+      <c r="CB56" s="40"/>
+      <c r="CC56" s="41"/>
+      <c r="CD56" s="40"/>
+      <c r="CE56" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="CF56" s="39"/>
+      <c r="CG56" s="39"/>
+      <c r="CH56" s="39"/>
+      <c r="CI56" s="39"/>
+      <c r="CJ56" s="40"/>
     </row>
     <row r="57" spans="15:88">
       <c r="O57" s="6"/>
       <c r="Z57" s="6"/>
       <c r="AM57" s="6"/>
       <c r="AW57" s="6"/>
-      <c r="AX57" s="42"/>
-      <c r="AY57" s="43"/>
-      <c r="AZ57" s="44"/>
-      <c r="BA57" s="42"/>
-      <c r="BB57" s="44"/>
-      <c r="BC57" s="43"/>
-      <c r="BD57" s="42"/>
-      <c r="BE57" s="42"/>
-      <c r="BF57" s="42"/>
-      <c r="BG57" s="42"/>
-      <c r="BH57" s="42"/>
-      <c r="BI57" s="42"/>
-      <c r="BJ57" s="43"/>
-      <c r="BK57" s="42"/>
-      <c r="BL57" s="42"/>
-      <c r="BM57" s="42"/>
-      <c r="BN57" s="42"/>
-      <c r="BO57" s="42"/>
-      <c r="BP57" s="42"/>
-      <c r="BQ57" s="42"/>
-      <c r="BR57" s="42"/>
-      <c r="BS57" s="42"/>
-      <c r="BT57" s="43"/>
-      <c r="BU57" s="44"/>
-      <c r="BV57" s="43"/>
-      <c r="BW57" s="42"/>
-      <c r="BX57" s="42"/>
-      <c r="BY57" s="42"/>
-      <c r="BZ57" s="42"/>
-      <c r="CA57" s="42"/>
-      <c r="CB57" s="43"/>
-      <c r="CC57" s="50"/>
-      <c r="CD57" s="51"/>
-      <c r="CE57" s="42"/>
-      <c r="CF57" s="42"/>
-      <c r="CG57" s="42"/>
-      <c r="CH57" s="42"/>
-      <c r="CI57" s="42"/>
-      <c r="CJ57" s="43"/>
+      <c r="AX57" s="39"/>
+      <c r="AY57" s="40"/>
+      <c r="AZ57" s="41"/>
+      <c r="BA57" s="39"/>
+      <c r="BB57" s="41"/>
+      <c r="BC57" s="40"/>
+      <c r="BD57" s="39"/>
+      <c r="BE57" s="39"/>
+      <c r="BF57" s="39"/>
+      <c r="BG57" s="39"/>
+      <c r="BH57" s="39"/>
+      <c r="BI57" s="39"/>
+      <c r="BJ57" s="40"/>
+      <c r="BK57" s="39"/>
+      <c r="BL57" s="39"/>
+      <c r="BM57" s="39"/>
+      <c r="BN57" s="39"/>
+      <c r="BO57" s="39"/>
+      <c r="BP57" s="39"/>
+      <c r="BQ57" s="39"/>
+      <c r="BR57" s="39"/>
+      <c r="BS57" s="39"/>
+      <c r="BT57" s="40"/>
+      <c r="BU57" s="41"/>
+      <c r="BV57" s="40"/>
+      <c r="BW57" s="39"/>
+      <c r="BX57" s="39"/>
+      <c r="BY57" s="39"/>
+      <c r="BZ57" s="39"/>
+      <c r="CA57" s="39"/>
+      <c r="CB57" s="40"/>
+      <c r="CC57" s="47"/>
+      <c r="CD57" s="48"/>
+      <c r="CE57" s="39"/>
+      <c r="CF57" s="39"/>
+      <c r="CG57" s="39"/>
+      <c r="CH57" s="39"/>
+      <c r="CI57" s="39"/>
+      <c r="CJ57" s="40"/>
     </row>
     <row r="58" spans="15:88">
       <c r="O58" s="6"/>
       <c r="Z58" s="6"/>
       <c r="AM58" s="6"/>
       <c r="AW58" s="6"/>
-      <c r="AX58" s="42"/>
-      <c r="AY58" s="43"/>
-      <c r="AZ58" s="44"/>
-      <c r="BA58" s="42"/>
-      <c r="BB58" s="44"/>
-      <c r="BC58" s="43"/>
-      <c r="BD58" s="42"/>
-      <c r="BE58" s="42"/>
-      <c r="BF58" s="42"/>
-      <c r="BG58" s="42"/>
-      <c r="BH58" s="42"/>
-      <c r="BI58" s="42"/>
-      <c r="BJ58" s="43"/>
-      <c r="BK58" s="42"/>
-      <c r="BL58" s="42"/>
-      <c r="BM58" s="42"/>
-      <c r="BN58" s="42"/>
-      <c r="BO58" s="42"/>
-      <c r="BP58" s="42"/>
-      <c r="BQ58" s="42"/>
-      <c r="BR58" s="42"/>
-      <c r="BS58" s="42"/>
-      <c r="BT58" s="43"/>
-      <c r="BU58" s="44"/>
-      <c r="BV58" s="43"/>
-      <c r="BW58" s="42"/>
-      <c r="BX58" s="42"/>
-      <c r="BY58" s="42"/>
-      <c r="BZ58" s="42"/>
-      <c r="CA58" s="42"/>
-      <c r="CB58" s="43"/>
-      <c r="CC58" s="42"/>
-      <c r="CD58" s="42"/>
-      <c r="CE58" s="42"/>
-      <c r="CF58" s="42"/>
-      <c r="CG58" s="42"/>
-      <c r="CH58" s="42"/>
-      <c r="CI58" s="42"/>
-      <c r="CJ58" s="43"/>
+      <c r="AX58" s="39"/>
+      <c r="AY58" s="40"/>
+      <c r="AZ58" s="41"/>
+      <c r="BA58" s="39"/>
+      <c r="BB58" s="41"/>
+      <c r="BC58" s="40"/>
+      <c r="BD58" s="39"/>
+      <c r="BE58" s="39"/>
+      <c r="BF58" s="39"/>
+      <c r="BG58" s="39"/>
+      <c r="BH58" s="39"/>
+      <c r="BI58" s="39"/>
+      <c r="BJ58" s="40"/>
+      <c r="BK58" s="39"/>
+      <c r="BL58" s="39"/>
+      <c r="BM58" s="39"/>
+      <c r="BN58" s="39"/>
+      <c r="BO58" s="39"/>
+      <c r="BP58" s="39"/>
+      <c r="BQ58" s="39"/>
+      <c r="BR58" s="39"/>
+      <c r="BS58" s="39"/>
+      <c r="BT58" s="40"/>
+      <c r="BU58" s="41"/>
+      <c r="BV58" s="40"/>
+      <c r="BW58" s="39"/>
+      <c r="BX58" s="39"/>
+      <c r="BY58" s="39"/>
+      <c r="BZ58" s="39"/>
+      <c r="CA58" s="39"/>
+      <c r="CB58" s="40"/>
+      <c r="CC58" s="39"/>
+      <c r="CD58" s="39"/>
+      <c r="CE58" s="39"/>
+      <c r="CF58" s="39"/>
+      <c r="CG58" s="39"/>
+      <c r="CH58" s="39"/>
+      <c r="CI58" s="39"/>
+      <c r="CJ58" s="40"/>
     </row>
     <row r="59" spans="15:88">
       <c r="O59" s="6"/>
       <c r="Z59" s="6"/>
       <c r="AM59" s="6"/>
       <c r="AW59" s="6"/>
-      <c r="AX59" s="42"/>
-      <c r="AY59" s="43"/>
-      <c r="AZ59" s="44"/>
-      <c r="BA59" s="42"/>
-      <c r="BB59" s="44"/>
-      <c r="BC59" s="43"/>
-      <c r="BD59" s="42"/>
-      <c r="BE59" s="42"/>
-      <c r="BF59" s="42"/>
-      <c r="BG59" s="42"/>
-      <c r="BH59" s="42"/>
-      <c r="BI59" s="42"/>
-      <c r="BJ59" s="43"/>
-      <c r="BK59" s="42"/>
-      <c r="BL59" s="42"/>
-      <c r="BM59" s="42"/>
-      <c r="BN59" s="42"/>
-      <c r="BO59" s="42"/>
-      <c r="BP59" s="42"/>
-      <c r="BQ59" s="42"/>
-      <c r="BR59" s="42"/>
-      <c r="BS59" s="42"/>
-      <c r="BT59" s="43"/>
-      <c r="BU59" s="44"/>
-      <c r="BV59" s="43"/>
-      <c r="BW59" s="42"/>
-      <c r="BX59" s="42"/>
-      <c r="BY59" s="42"/>
-      <c r="BZ59" s="42"/>
-      <c r="CA59" s="42"/>
-      <c r="CB59" s="43"/>
-      <c r="CC59" s="42"/>
-      <c r="CD59" s="42"/>
-      <c r="CE59" s="42"/>
-      <c r="CF59" s="42"/>
-      <c r="CG59" s="42"/>
-      <c r="CH59" s="42"/>
-      <c r="CI59" s="42"/>
-      <c r="CJ59" s="43"/>
+      <c r="AX59" s="39"/>
+      <c r="AY59" s="40"/>
+      <c r="AZ59" s="41"/>
+      <c r="BA59" s="39"/>
+      <c r="BB59" s="41"/>
+      <c r="BC59" s="40"/>
+      <c r="BD59" s="39"/>
+      <c r="BE59" s="39"/>
+      <c r="BF59" s="39"/>
+      <c r="BG59" s="39"/>
+      <c r="BH59" s="39"/>
+      <c r="BI59" s="39"/>
+      <c r="BJ59" s="40"/>
+      <c r="BK59" s="39"/>
+      <c r="BL59" s="39"/>
+      <c r="BM59" s="39"/>
+      <c r="BN59" s="39"/>
+      <c r="BO59" s="39"/>
+      <c r="BP59" s="39"/>
+      <c r="BQ59" s="39"/>
+      <c r="BR59" s="39"/>
+      <c r="BS59" s="39"/>
+      <c r="BT59" s="40"/>
+      <c r="BU59" s="41"/>
+      <c r="BV59" s="40"/>
+      <c r="BW59" s="39"/>
+      <c r="BX59" s="39"/>
+      <c r="BY59" s="39"/>
+      <c r="BZ59" s="39"/>
+      <c r="CA59" s="39"/>
+      <c r="CB59" s="40"/>
+      <c r="CC59" s="39"/>
+      <c r="CD59" s="39"/>
+      <c r="CE59" s="39"/>
+      <c r="CF59" s="39"/>
+      <c r="CG59" s="39"/>
+      <c r="CH59" s="39"/>
+      <c r="CI59" s="39"/>
+      <c r="CJ59" s="40"/>
     </row>
     <row r="60" spans="15:88">
       <c r="O60" s="6"/>
       <c r="Z60" s="6"/>
       <c r="AM60" s="6"/>
       <c r="AW60" s="6"/>
-      <c r="AX60" s="42"/>
-      <c r="AY60" s="43"/>
-      <c r="AZ60" s="44"/>
-      <c r="BA60" s="42"/>
-      <c r="BB60" s="44"/>
-      <c r="BC60" s="43"/>
-      <c r="BD60" s="42"/>
-      <c r="BE60" s="42"/>
-      <c r="BF60" s="42"/>
-      <c r="BG60" s="42"/>
-      <c r="BH60" s="42"/>
-      <c r="BI60" s="42"/>
-      <c r="BJ60" s="43"/>
-      <c r="BK60" s="42"/>
-      <c r="BL60" s="42"/>
-      <c r="BM60" s="42"/>
-      <c r="BN60" s="42"/>
-      <c r="BO60" s="42"/>
-      <c r="BP60" s="42"/>
-      <c r="BQ60" s="42"/>
-      <c r="BR60" s="42"/>
-      <c r="BS60" s="42"/>
-      <c r="BT60" s="43"/>
-      <c r="BU60" s="44"/>
-      <c r="BV60" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="BW60" s="42"/>
-      <c r="BX60" s="42"/>
-      <c r="BY60" s="42"/>
-      <c r="BZ60" s="42"/>
-      <c r="CA60" s="42"/>
-      <c r="CB60" s="43" t="s">
-        <v>76</v>
-      </c>
-      <c r="CC60" s="42"/>
-      <c r="CD60" s="42"/>
-      <c r="CE60" s="42"/>
-      <c r="CF60" s="42"/>
-      <c r="CG60" s="42"/>
-      <c r="CH60" s="42"/>
-      <c r="CI60" s="42"/>
-      <c r="CJ60" s="43"/>
+      <c r="AX60" s="39"/>
+      <c r="AY60" s="40"/>
+      <c r="AZ60" s="41"/>
+      <c r="BA60" s="39"/>
+      <c r="BB60" s="41"/>
+      <c r="BC60" s="40"/>
+      <c r="BD60" s="39"/>
+      <c r="BE60" s="39"/>
+      <c r="BF60" s="39"/>
+      <c r="BG60" s="39"/>
+      <c r="BH60" s="39"/>
+      <c r="BI60" s="39"/>
+      <c r="BJ60" s="40"/>
+      <c r="BK60" s="39"/>
+      <c r="BL60" s="39"/>
+      <c r="BM60" s="39"/>
+      <c r="BN60" s="39"/>
+      <c r="BO60" s="39"/>
+      <c r="BP60" s="39"/>
+      <c r="BQ60" s="39"/>
+      <c r="BR60" s="39"/>
+      <c r="BS60" s="39"/>
+      <c r="BT60" s="40"/>
+      <c r="BU60" s="41"/>
+      <c r="BV60" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="BW60" s="39"/>
+      <c r="BX60" s="39"/>
+      <c r="BY60" s="39"/>
+      <c r="BZ60" s="39"/>
+      <c r="CA60" s="39"/>
+      <c r="CB60" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="CC60" s="39"/>
+      <c r="CD60" s="39"/>
+      <c r="CE60" s="39"/>
+      <c r="CF60" s="39"/>
+      <c r="CG60" s="39"/>
+      <c r="CH60" s="39"/>
+      <c r="CI60" s="39"/>
+      <c r="CJ60" s="40"/>
     </row>
     <row r="61" spans="15:88">
       <c r="O61" s="6"/>
       <c r="Z61" s="6"/>
       <c r="AM61" s="6"/>
       <c r="AW61" s="6"/>
-      <c r="AX61" s="42"/>
-      <c r="AY61" s="43"/>
-      <c r="AZ61" s="44"/>
-      <c r="BA61" s="42"/>
-      <c r="BB61" s="44"/>
-      <c r="BC61" s="43"/>
-      <c r="BD61" s="42"/>
-      <c r="BE61" s="42"/>
-      <c r="BF61" s="42"/>
-      <c r="BG61" s="42"/>
-      <c r="BH61" s="42"/>
-      <c r="BI61" s="42"/>
-      <c r="BJ61" s="43"/>
-      <c r="BK61" s="42"/>
-      <c r="BL61" s="42"/>
-      <c r="BM61" s="42"/>
-      <c r="BN61" s="42"/>
-      <c r="BO61" s="42"/>
-      <c r="BP61" s="42"/>
-      <c r="BQ61" s="42"/>
-      <c r="BR61" s="42"/>
-      <c r="BS61" s="42"/>
-      <c r="BT61" s="43"/>
-      <c r="BU61" s="44"/>
-      <c r="BV61" s="43"/>
-      <c r="BW61" s="42"/>
-      <c r="BX61" s="42"/>
-      <c r="BY61" s="42"/>
-      <c r="BZ61" s="42"/>
-      <c r="CA61" s="42"/>
-      <c r="CB61" s="43"/>
-      <c r="CC61" s="46"/>
-      <c r="CD61" s="47"/>
-      <c r="CE61" s="47"/>
-      <c r="CF61" s="48"/>
-      <c r="CG61" s="42"/>
-      <c r="CH61" s="42"/>
-      <c r="CI61" s="42"/>
-      <c r="CJ61" s="43"/>
+      <c r="AX61" s="39"/>
+      <c r="AY61" s="40"/>
+      <c r="AZ61" s="41"/>
+      <c r="BA61" s="39"/>
+      <c r="BB61" s="41"/>
+      <c r="BC61" s="40"/>
+      <c r="BD61" s="39"/>
+      <c r="BE61" s="39"/>
+      <c r="BF61" s="39"/>
+      <c r="BG61" s="39"/>
+      <c r="BH61" s="39"/>
+      <c r="BI61" s="39"/>
+      <c r="BJ61" s="40"/>
+      <c r="BK61" s="39"/>
+      <c r="BL61" s="39"/>
+      <c r="BM61" s="39"/>
+      <c r="BN61" s="39"/>
+      <c r="BO61" s="39"/>
+      <c r="BP61" s="39"/>
+      <c r="BQ61" s="39"/>
+      <c r="BR61" s="39"/>
+      <c r="BS61" s="39"/>
+      <c r="BT61" s="40"/>
+      <c r="BU61" s="41"/>
+      <c r="BV61" s="40"/>
+      <c r="BW61" s="39"/>
+      <c r="BX61" s="39"/>
+      <c r="BY61" s="39"/>
+      <c r="BZ61" s="39"/>
+      <c r="CA61" s="39"/>
+      <c r="CB61" s="40"/>
+      <c r="CC61" s="43"/>
+      <c r="CD61" s="44"/>
+      <c r="CE61" s="44"/>
+      <c r="CF61" s="45"/>
+      <c r="CG61" s="39"/>
+      <c r="CH61" s="39"/>
+      <c r="CI61" s="39"/>
+      <c r="CJ61" s="40"/>
     </row>
     <row r="62" spans="15:88">
       <c r="O62" s="6"/>
       <c r="Z62" s="6"/>
       <c r="AM62" s="6"/>
       <c r="AW62" s="6"/>
-      <c r="AX62" s="42"/>
-      <c r="AY62" s="43"/>
-      <c r="AZ62" s="44"/>
-      <c r="BA62" s="42"/>
-      <c r="BB62" s="44"/>
-      <c r="BC62" s="43"/>
-      <c r="BD62" s="42"/>
-      <c r="BE62" s="42"/>
-      <c r="BF62" s="42"/>
-      <c r="BG62" s="42"/>
-      <c r="BH62" s="42"/>
-      <c r="BI62" s="42"/>
-      <c r="BJ62" s="43"/>
-      <c r="BK62" s="42"/>
-      <c r="BL62" s="42"/>
-      <c r="BM62" s="42"/>
-      <c r="BN62" s="42"/>
-      <c r="BO62" s="42"/>
-      <c r="BP62" s="42"/>
-      <c r="BQ62" s="42"/>
-      <c r="BR62" s="42"/>
-      <c r="BS62" s="42"/>
-      <c r="BT62" s="43"/>
-      <c r="BU62" s="44"/>
-      <c r="BV62" s="43"/>
-      <c r="BW62" s="42"/>
-      <c r="BX62" s="42"/>
-      <c r="BY62" s="42"/>
-      <c r="BZ62" s="42"/>
-      <c r="CA62" s="42"/>
-      <c r="CB62" s="43"/>
-      <c r="CC62" s="40"/>
-      <c r="CD62" s="41"/>
-      <c r="CE62" s="40"/>
-      <c r="CF62" s="42"/>
-      <c r="CG62" s="42"/>
-      <c r="CH62" s="42"/>
-      <c r="CI62" s="42"/>
-      <c r="CJ62" s="43"/>
+      <c r="AX62" s="39"/>
+      <c r="AY62" s="40"/>
+      <c r="AZ62" s="41"/>
+      <c r="BA62" s="39"/>
+      <c r="BB62" s="41"/>
+      <c r="BC62" s="40"/>
+      <c r="BD62" s="39"/>
+      <c r="BE62" s="39"/>
+      <c r="BF62" s="39"/>
+      <c r="BG62" s="39"/>
+      <c r="BH62" s="39"/>
+      <c r="BI62" s="39"/>
+      <c r="BJ62" s="40"/>
+      <c r="BK62" s="39"/>
+      <c r="BL62" s="39"/>
+      <c r="BM62" s="39"/>
+      <c r="BN62" s="39"/>
+      <c r="BO62" s="39"/>
+      <c r="BP62" s="39"/>
+      <c r="BQ62" s="39"/>
+      <c r="BR62" s="39"/>
+      <c r="BS62" s="39"/>
+      <c r="BT62" s="40"/>
+      <c r="BU62" s="41"/>
+      <c r="BV62" s="40"/>
+      <c r="BW62" s="39"/>
+      <c r="BX62" s="39"/>
+      <c r="BY62" s="39"/>
+      <c r="BZ62" s="39"/>
+      <c r="CA62" s="39"/>
+      <c r="CB62" s="40"/>
+      <c r="CC62" s="37"/>
+      <c r="CD62" s="38"/>
+      <c r="CE62" s="37"/>
+      <c r="CF62" s="39"/>
+      <c r="CG62" s="39"/>
+      <c r="CH62" s="39"/>
+      <c r="CI62" s="39"/>
+      <c r="CJ62" s="40"/>
     </row>
     <row r="63" spans="15:88">
       <c r="O63" s="6"/>
       <c r="Z63" s="6"/>
       <c r="AM63" s="6"/>
       <c r="AW63" s="6"/>
-      <c r="AX63" s="42"/>
-      <c r="AY63" s="43"/>
-      <c r="AZ63" s="44"/>
-      <c r="BA63" s="42"/>
-      <c r="BB63" s="44"/>
-      <c r="BC63" s="43"/>
-      <c r="BD63" s="42"/>
-      <c r="BE63" s="42"/>
-      <c r="BF63" s="42"/>
-      <c r="BG63" s="42"/>
-      <c r="BH63" s="42"/>
-      <c r="BI63" s="42"/>
-      <c r="BJ63" s="43"/>
-      <c r="BK63" s="42"/>
-      <c r="BL63" s="42"/>
-      <c r="BM63" s="42"/>
-      <c r="BN63" s="42"/>
-      <c r="BO63" s="42"/>
-      <c r="BP63" s="42"/>
-      <c r="BQ63" s="42"/>
-      <c r="BR63" s="42"/>
-      <c r="BS63" s="42"/>
-      <c r="BT63" s="43"/>
-      <c r="BU63" s="44"/>
-      <c r="BV63" s="43"/>
-      <c r="BW63" s="42"/>
-      <c r="BX63" s="42"/>
-      <c r="BY63" s="42"/>
-      <c r="BZ63" s="42"/>
-      <c r="CA63" s="42"/>
-      <c r="CB63" s="43"/>
-      <c r="CC63" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="CD63" s="42"/>
-      <c r="CE63" s="42"/>
-      <c r="CF63" s="42"/>
-      <c r="CG63" s="42"/>
-      <c r="CH63" s="42"/>
-      <c r="CI63" s="42"/>
-      <c r="CJ63" s="43"/>
+      <c r="AX63" s="39"/>
+      <c r="AY63" s="40"/>
+      <c r="AZ63" s="41"/>
+      <c r="BA63" s="39"/>
+      <c r="BB63" s="41"/>
+      <c r="BC63" s="40"/>
+      <c r="BD63" s="39"/>
+      <c r="BE63" s="39"/>
+      <c r="BF63" s="39"/>
+      <c r="BG63" s="39"/>
+      <c r="BH63" s="39"/>
+      <c r="BI63" s="39"/>
+      <c r="BJ63" s="40"/>
+      <c r="BK63" s="39"/>
+      <c r="BL63" s="39"/>
+      <c r="BM63" s="39"/>
+      <c r="BN63" s="39"/>
+      <c r="BO63" s="39"/>
+      <c r="BP63" s="39"/>
+      <c r="BQ63" s="39"/>
+      <c r="BR63" s="39"/>
+      <c r="BS63" s="39"/>
+      <c r="BT63" s="40"/>
+      <c r="BU63" s="41"/>
+      <c r="BV63" s="40"/>
+      <c r="BW63" s="39"/>
+      <c r="BX63" s="39"/>
+      <c r="BY63" s="39"/>
+      <c r="BZ63" s="39"/>
+      <c r="CA63" s="39"/>
+      <c r="CB63" s="40"/>
+      <c r="CC63" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="CD63" s="39"/>
+      <c r="CE63" s="39"/>
+      <c r="CF63" s="39"/>
+      <c r="CG63" s="39"/>
+      <c r="CH63" s="39"/>
+      <c r="CI63" s="39"/>
+      <c r="CJ63" s="40"/>
     </row>
     <row r="64" spans="15:88">
       <c r="O64" s="6"/>
       <c r="Z64" s="6"/>
       <c r="AM64" s="6"/>
       <c r="AW64" s="6"/>
-      <c r="AX64" s="42"/>
-      <c r="AY64" s="43"/>
-      <c r="AZ64" s="44"/>
-      <c r="BA64" s="42"/>
-      <c r="BB64" s="44"/>
-      <c r="BC64" s="43"/>
-      <c r="BD64" s="42"/>
-      <c r="BE64" s="42"/>
-      <c r="BF64" s="42"/>
-      <c r="BG64" s="42"/>
-      <c r="BH64" s="42"/>
-      <c r="BI64" s="42"/>
-      <c r="BJ64" s="43"/>
-      <c r="BK64" s="42"/>
-      <c r="BL64" s="42"/>
-      <c r="BM64" s="42"/>
-      <c r="BN64" s="42"/>
-      <c r="BO64" s="42"/>
-      <c r="BP64" s="42"/>
-      <c r="BQ64" s="42"/>
-      <c r="BR64" s="42"/>
-      <c r="BS64" s="42"/>
-      <c r="BT64" s="43"/>
-      <c r="BU64" s="44"/>
-      <c r="BV64" s="43"/>
-      <c r="BW64" s="42"/>
-      <c r="BX64" s="42"/>
-      <c r="BY64" s="42"/>
-      <c r="BZ64" s="42"/>
-      <c r="CA64" s="42"/>
-      <c r="CB64" s="43"/>
-      <c r="CC64" s="50"/>
-      <c r="CD64" s="51"/>
-      <c r="CE64" s="42"/>
-      <c r="CF64" s="42"/>
-      <c r="CG64" s="42"/>
-      <c r="CH64" s="42"/>
-      <c r="CI64" s="42"/>
-      <c r="CJ64" s="43"/>
+      <c r="AX64" s="39"/>
+      <c r="AY64" s="40"/>
+      <c r="AZ64" s="41"/>
+      <c r="BA64" s="39"/>
+      <c r="BB64" s="41"/>
+      <c r="BC64" s="40"/>
+      <c r="BD64" s="39"/>
+      <c r="BE64" s="39"/>
+      <c r="BF64" s="39"/>
+      <c r="BG64" s="39"/>
+      <c r="BH64" s="39"/>
+      <c r="BI64" s="39"/>
+      <c r="BJ64" s="40"/>
+      <c r="BK64" s="39"/>
+      <c r="BL64" s="39"/>
+      <c r="BM64" s="39"/>
+      <c r="BN64" s="39"/>
+      <c r="BO64" s="39"/>
+      <c r="BP64" s="39"/>
+      <c r="BQ64" s="39"/>
+      <c r="BR64" s="39"/>
+      <c r="BS64" s="39"/>
+      <c r="BT64" s="40"/>
+      <c r="BU64" s="41"/>
+      <c r="BV64" s="40"/>
+      <c r="BW64" s="39"/>
+      <c r="BX64" s="39"/>
+      <c r="BY64" s="39"/>
+      <c r="BZ64" s="39"/>
+      <c r="CA64" s="39"/>
+      <c r="CB64" s="40"/>
+      <c r="CC64" s="47"/>
+      <c r="CD64" s="48"/>
+      <c r="CE64" s="39"/>
+      <c r="CF64" s="39"/>
+      <c r="CG64" s="39"/>
+      <c r="CH64" s="39"/>
+      <c r="CI64" s="39"/>
+      <c r="CJ64" s="40"/>
     </row>
     <row r="65" spans="15:88">
       <c r="O65" s="6"/>
       <c r="Z65" s="6"/>
       <c r="AM65" s="6"/>
       <c r="AW65" s="6"/>
-      <c r="AX65" s="42"/>
-      <c r="AY65" s="43"/>
-      <c r="AZ65" s="44"/>
-      <c r="BA65" s="43"/>
-      <c r="BB65" s="44"/>
-      <c r="BC65" s="43"/>
-      <c r="BD65" s="42"/>
-      <c r="BE65" s="42"/>
-      <c r="BF65" s="42"/>
-      <c r="BG65" s="42"/>
-      <c r="BH65" s="42"/>
-      <c r="BI65" s="42"/>
-      <c r="BJ65" s="43"/>
-      <c r="BK65" s="42"/>
-      <c r="BL65" s="42"/>
-      <c r="BM65" s="42"/>
-      <c r="BN65" s="42"/>
-      <c r="BO65" s="42"/>
-      <c r="BP65" s="42"/>
-      <c r="BQ65" s="42"/>
-      <c r="BR65" s="42"/>
-      <c r="BS65" s="42"/>
-      <c r="BT65" s="43"/>
-      <c r="BU65" s="50"/>
-      <c r="BV65" s="51"/>
-      <c r="BW65" s="42"/>
-      <c r="BX65" s="42"/>
-      <c r="BY65" s="42"/>
-      <c r="BZ65" s="42"/>
-      <c r="CA65" s="42"/>
-      <c r="CB65" s="43"/>
-      <c r="CC65" s="42"/>
-      <c r="CD65" s="42"/>
-      <c r="CE65" s="42"/>
-      <c r="CF65" s="42"/>
-      <c r="CG65" s="42"/>
-      <c r="CH65" s="42"/>
-      <c r="CI65" s="42"/>
-      <c r="CJ65" s="43"/>
+      <c r="AX65" s="39"/>
+      <c r="AY65" s="40"/>
+      <c r="AZ65" s="41"/>
+      <c r="BA65" s="40"/>
+      <c r="BB65" s="41"/>
+      <c r="BC65" s="40"/>
+      <c r="BD65" s="39"/>
+      <c r="BE65" s="39"/>
+      <c r="BF65" s="39"/>
+      <c r="BG65" s="39"/>
+      <c r="BH65" s="39"/>
+      <c r="BI65" s="39"/>
+      <c r="BJ65" s="40"/>
+      <c r="BK65" s="39"/>
+      <c r="BL65" s="39"/>
+      <c r="BM65" s="39"/>
+      <c r="BN65" s="39"/>
+      <c r="BO65" s="39"/>
+      <c r="BP65" s="39"/>
+      <c r="BQ65" s="39"/>
+      <c r="BR65" s="39"/>
+      <c r="BS65" s="39"/>
+      <c r="BT65" s="40"/>
+      <c r="BU65" s="47"/>
+      <c r="BV65" s="48"/>
+      <c r="BW65" s="39"/>
+      <c r="BX65" s="39"/>
+      <c r="BY65" s="39"/>
+      <c r="BZ65" s="39"/>
+      <c r="CA65" s="39"/>
+      <c r="CB65" s="40"/>
+      <c r="CC65" s="39"/>
+      <c r="CD65" s="39"/>
+      <c r="CE65" s="39"/>
+      <c r="CF65" s="39"/>
+      <c r="CG65" s="39"/>
+      <c r="CH65" s="39"/>
+      <c r="CI65" s="39"/>
+      <c r="CJ65" s="40"/>
     </row>
     <row r="66" spans="15:88">
       <c r="O66" s="6"/>
       <c r="Z66" s="6"/>
       <c r="AM66" s="6"/>
       <c r="AW66" s="6"/>
-      <c r="AX66" s="42"/>
-      <c r="AY66" s="43"/>
-      <c r="AZ66" s="44"/>
-      <c r="BA66" s="43"/>
-      <c r="BB66" s="44"/>
-      <c r="BC66" s="43"/>
-      <c r="BD66" s="42"/>
-      <c r="BE66" s="42"/>
-      <c r="BF66" s="42"/>
-      <c r="BG66" s="42"/>
-      <c r="BH66" s="42"/>
-      <c r="BI66" s="42"/>
-      <c r="BJ66" s="43"/>
-      <c r="BK66" s="42"/>
-      <c r="BL66" s="42"/>
-      <c r="BM66" s="42"/>
-      <c r="BN66" s="42"/>
-      <c r="BO66" s="42"/>
-      <c r="BP66" s="42"/>
-      <c r="BQ66" s="42"/>
-      <c r="BR66" s="42"/>
-      <c r="BS66" s="42"/>
-      <c r="BT66" s="43"/>
-      <c r="BU66" s="42"/>
-      <c r="BV66" s="42"/>
-      <c r="BW66" s="42"/>
-      <c r="BX66" s="42"/>
-      <c r="BY66" s="42"/>
-      <c r="BZ66" s="42"/>
-      <c r="CA66" s="42"/>
-      <c r="CB66" s="43"/>
-      <c r="CC66" s="42"/>
-      <c r="CD66" s="42"/>
-      <c r="CE66" s="42"/>
-      <c r="CF66" s="42"/>
-      <c r="CG66" s="42"/>
-      <c r="CH66" s="42"/>
-      <c r="CI66" s="42"/>
-      <c r="CJ66" s="43"/>
+      <c r="AX66" s="39"/>
+      <c r="AY66" s="40"/>
+      <c r="AZ66" s="41"/>
+      <c r="BA66" s="40"/>
+      <c r="BB66" s="41"/>
+      <c r="BC66" s="40"/>
+      <c r="BD66" s="39"/>
+      <c r="BE66" s="39"/>
+      <c r="BF66" s="39"/>
+      <c r="BG66" s="39"/>
+      <c r="BH66" s="39"/>
+      <c r="BI66" s="39"/>
+      <c r="BJ66" s="40"/>
+      <c r="BK66" s="39"/>
+      <c r="BL66" s="39"/>
+      <c r="BM66" s="39"/>
+      <c r="BN66" s="39"/>
+      <c r="BO66" s="39"/>
+      <c r="BP66" s="39"/>
+      <c r="BQ66" s="39"/>
+      <c r="BR66" s="39"/>
+      <c r="BS66" s="39"/>
+      <c r="BT66" s="40"/>
+      <c r="BU66" s="39"/>
+      <c r="BV66" s="39"/>
+      <c r="BW66" s="39"/>
+      <c r="BX66" s="39"/>
+      <c r="BY66" s="39"/>
+      <c r="BZ66" s="39"/>
+      <c r="CA66" s="39"/>
+      <c r="CB66" s="40"/>
+      <c r="CC66" s="39"/>
+      <c r="CD66" s="39"/>
+      <c r="CE66" s="39"/>
+      <c r="CF66" s="39"/>
+      <c r="CG66" s="39"/>
+      <c r="CH66" s="39"/>
+      <c r="CI66" s="39"/>
+      <c r="CJ66" s="40"/>
     </row>
     <row r="67" spans="15:88">
       <c r="O67" s="6"/>
       <c r="Z67" s="6"/>
       <c r="AM67" s="6"/>
       <c r="AW67" s="6"/>
-      <c r="AX67" s="42"/>
-      <c r="AY67" s="43"/>
-      <c r="AZ67" s="44"/>
-      <c r="BA67" s="43"/>
-      <c r="BB67" s="45"/>
-      <c r="BC67" s="51"/>
-      <c r="BD67" s="42"/>
-      <c r="BE67" s="42"/>
-      <c r="BF67" s="42"/>
-      <c r="BG67" s="42"/>
-      <c r="BH67" s="42"/>
-      <c r="BI67" s="42"/>
-      <c r="BJ67" s="43"/>
-      <c r="BK67" s="42"/>
-      <c r="BL67" s="42"/>
-      <c r="BM67" s="42"/>
-      <c r="BN67" s="42"/>
-      <c r="BO67" s="42"/>
-      <c r="BP67" s="42"/>
-      <c r="BQ67" s="42"/>
-      <c r="BR67" s="42"/>
-      <c r="BS67" s="42"/>
-      <c r="BT67" s="43"/>
-      <c r="BU67" s="42"/>
-      <c r="BV67" s="42"/>
-      <c r="BW67" s="42"/>
-      <c r="BX67" s="42"/>
-      <c r="BY67" s="42"/>
-      <c r="BZ67" s="42"/>
-      <c r="CA67" s="42"/>
-      <c r="CB67" s="43"/>
-      <c r="CC67" s="42"/>
-      <c r="CD67" s="42"/>
-      <c r="CE67" s="42"/>
-      <c r="CF67" s="42"/>
-      <c r="CG67" s="42"/>
-      <c r="CH67" s="42"/>
-      <c r="CI67" s="42"/>
-      <c r="CJ67" s="43"/>
+      <c r="AX67" s="39"/>
+      <c r="AY67" s="40"/>
+      <c r="AZ67" s="41"/>
+      <c r="BA67" s="40"/>
+      <c r="BB67" s="42"/>
+      <c r="BC67" s="48"/>
+      <c r="BD67" s="39"/>
+      <c r="BE67" s="39"/>
+      <c r="BF67" s="39"/>
+      <c r="BG67" s="39"/>
+      <c r="BH67" s="39"/>
+      <c r="BI67" s="39"/>
+      <c r="BJ67" s="40"/>
+      <c r="BK67" s="39"/>
+      <c r="BL67" s="39"/>
+      <c r="BM67" s="39"/>
+      <c r="BN67" s="39"/>
+      <c r="BO67" s="39"/>
+      <c r="BP67" s="39"/>
+      <c r="BQ67" s="39"/>
+      <c r="BR67" s="39"/>
+      <c r="BS67" s="39"/>
+      <c r="BT67" s="40"/>
+      <c r="BU67" s="39"/>
+      <c r="BV67" s="39"/>
+      <c r="BW67" s="39"/>
+      <c r="BX67" s="39"/>
+      <c r="BY67" s="39"/>
+      <c r="BZ67" s="39"/>
+      <c r="CA67" s="39"/>
+      <c r="CB67" s="40"/>
+      <c r="CC67" s="39"/>
+      <c r="CD67" s="39"/>
+      <c r="CE67" s="39"/>
+      <c r="CF67" s="39"/>
+      <c r="CG67" s="39"/>
+      <c r="CH67" s="39"/>
+      <c r="CI67" s="39"/>
+      <c r="CJ67" s="40"/>
     </row>
     <row r="68" spans="15:88">
       <c r="O68" s="6"/>
       <c r="Z68" s="6"/>
       <c r="AM68" s="6"/>
       <c r="AW68" s="6"/>
-      <c r="AX68" s="42"/>
-      <c r="AY68" s="51"/>
-      <c r="AZ68" s="50"/>
-      <c r="BA68" s="51"/>
-      <c r="BB68" s="45"/>
-      <c r="BC68" s="45"/>
-      <c r="BD68" s="45"/>
-      <c r="BE68" s="45"/>
-      <c r="BF68" s="45"/>
-      <c r="BG68" s="45"/>
-      <c r="BH68" s="45"/>
-      <c r="BI68" s="45"/>
-      <c r="BJ68" s="51"/>
-      <c r="BK68" s="45"/>
-      <c r="BL68" s="45"/>
-      <c r="BM68" s="45"/>
-      <c r="BN68" s="45"/>
-      <c r="BO68" s="45"/>
-      <c r="BP68" s="45"/>
-      <c r="BQ68" s="45"/>
-      <c r="BR68" s="45"/>
-      <c r="BS68" s="45"/>
-      <c r="BT68" s="51"/>
-      <c r="BU68" s="45"/>
-      <c r="BV68" s="45"/>
-      <c r="BW68" s="45"/>
-      <c r="BX68" s="45"/>
-      <c r="BY68" s="45"/>
-      <c r="BZ68" s="45"/>
-      <c r="CA68" s="45"/>
-      <c r="CB68" s="51"/>
-      <c r="CC68" s="45"/>
-      <c r="CD68" s="45"/>
-      <c r="CE68" s="45"/>
-      <c r="CF68" s="45"/>
-      <c r="CG68" s="45"/>
-      <c r="CH68" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="CI68" s="45"/>
-      <c r="CJ68" s="51"/>
+      <c r="AX68" s="39"/>
+      <c r="AY68" s="48"/>
+      <c r="AZ68" s="47"/>
+      <c r="BA68" s="48"/>
+      <c r="BB68" s="42"/>
+      <c r="BC68" s="42"/>
+      <c r="BD68" s="42"/>
+      <c r="BE68" s="42"/>
+      <c r="BF68" s="42"/>
+      <c r="BG68" s="42"/>
+      <c r="BH68" s="42"/>
+      <c r="BI68" s="42"/>
+      <c r="BJ68" s="48"/>
+      <c r="BK68" s="42"/>
+      <c r="BL68" s="42"/>
+      <c r="BM68" s="42"/>
+      <c r="BN68" s="42"/>
+      <c r="BO68" s="42"/>
+      <c r="BP68" s="42"/>
+      <c r="BQ68" s="42"/>
+      <c r="BR68" s="42"/>
+      <c r="BS68" s="42"/>
+      <c r="BT68" s="48"/>
+      <c r="BU68" s="42"/>
+      <c r="BV68" s="42"/>
+      <c r="BW68" s="42"/>
+      <c r="BX68" s="42"/>
+      <c r="BY68" s="42"/>
+      <c r="BZ68" s="42"/>
+      <c r="CA68" s="42"/>
+      <c r="CB68" s="48"/>
+      <c r="CC68" s="42"/>
+      <c r="CD68" s="42"/>
+      <c r="CE68" s="42"/>
+      <c r="CF68" s="42"/>
+      <c r="CG68" s="42"/>
+      <c r="CH68" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="CI68" s="42"/>
+      <c r="CJ68" s="48"/>
     </row>
     <row r="69" spans="15:88">
       <c r="O69" s="6"/>
@@ -9061,26 +9776,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A20:BM114"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="20" spans="2:15">
-      <c r="B20" s="52" t="s">
-        <v>82</v>
+      <c r="B20" s="49" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="2:15">
-      <c r="B21" s="53" t="s">
-        <v>83</v>
+      <c r="B21" s="50" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="2:15">
       <c r="B22" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="2:15">
       <c r="C24" s="13" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
@@ -9093,113 +9808,113 @@
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
-      <c r="O24" s="54"/>
+      <c r="O24" s="51"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="C25" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="56"/>
-      <c r="L25" s="56"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="57"/>
+      <c r="C25" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="54"/>
     </row>
     <row r="26" spans="2:15">
-      <c r="C26" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="56"/>
-      <c r="O26" s="57"/>
+      <c r="C26" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="54"/>
     </row>
     <row r="27" spans="2:15">
-      <c r="C27" s="55" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="57"/>
+      <c r="C27" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="54"/>
     </row>
     <row r="28" spans="2:15">
-      <c r="C28" s="55" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="56"/>
-      <c r="M28" s="56"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="57"/>
+      <c r="C28" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="54"/>
     </row>
     <row r="29" spans="2:15">
-      <c r="C29" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="57"/>
+      <c r="C29" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="54"/>
     </row>
     <row r="30" spans="2:15">
-      <c r="C30" s="55" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="57"/>
+      <c r="C30" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="54"/>
     </row>
     <row r="31" spans="2:15">
       <c r="C31" s="15" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
@@ -9212,45 +9927,45 @@
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
-      <c r="O31" s="58"/>
+      <c r="O31" s="55"/>
     </row>
     <row r="33" spans="2:44">
       <c r="B33" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="2:44" ht="18.75">
-      <c r="B34" s="59" t="s">
-        <v>94</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="2:44" ht="18">
+      <c r="B34" s="56" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="2:44">
-      <c r="F37" s="88" t="s">
-        <v>73</v>
-      </c>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="89"/>
-      <c r="K37" s="90"/>
-      <c r="N37" s="88" t="s">
-        <v>75</v>
-      </c>
-      <c r="O37" s="89"/>
-      <c r="P37" s="89"/>
-      <c r="Q37" s="89"/>
-      <c r="R37" s="89"/>
-      <c r="S37" s="90"/>
+      <c r="F37" s="85" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37" s="86"/>
+      <c r="H37" s="86"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="86"/>
+      <c r="K37" s="87"/>
+      <c r="N37" s="85" t="s">
+        <v>67</v>
+      </c>
+      <c r="O37" s="86"/>
+      <c r="P37" s="86"/>
+      <c r="Q37" s="86"/>
+      <c r="R37" s="86"/>
+      <c r="S37" s="87"/>
       <c r="Y37" s="10"/>
       <c r="Z37" s="11" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AA37" s="11"/>
       <c r="AB37" s="11"/>
       <c r="AC37" s="11"/>
       <c r="AD37" s="12"/>
       <c r="AO37" s="10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="AP37" s="11"/>
       <c r="AQ37" s="11"/>
@@ -9269,14 +9984,14 @@
       <c r="AP39" s="6"/>
     </row>
     <row r="40" spans="2:44">
-      <c r="C40" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="62"/>
+      <c r="C40" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="59"/>
       <c r="H40" s="6" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="P40" s="6"/>
       <c r="AA40" s="6"/>
@@ -9304,10 +10019,10 @@
       <c r="H43" s="6"/>
       <c r="I43" s="5"/>
       <c r="J43" s="6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AA43" s="6"/>
       <c r="AP43" s="6"/>
@@ -9341,7 +10056,7 @@
       <c r="P46" s="6"/>
       <c r="Q46" s="5"/>
       <c r="R46" s="6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AA46" s="6"/>
       <c r="AP46" s="6"/>
@@ -9356,17 +10071,17 @@
       <c r="AA47" s="6"/>
       <c r="AP47" s="6"/>
     </row>
-    <row r="48" spans="2:44">
+    <row r="48" spans="2:44" ht="15">
       <c r="H48" s="6"/>
       <c r="I48" s="5"/>
       <c r="J48" s="6"/>
       <c r="P48" s="6"/>
       <c r="Q48" s="5"/>
       <c r="R48" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA48" s="63" t="s">
-        <v>103</v>
+        <v>93</v>
+      </c>
+      <c r="AA48" s="60" t="s">
+        <v>95</v>
       </c>
       <c r="AP48" s="6"/>
     </row>
@@ -9406,7 +10121,7 @@
       <c r="AA51" s="6"/>
       <c r="AB51" s="5"/>
       <c r="AC51" s="6" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="AP51" s="6"/>
     </row>
@@ -9421,7 +10136,7 @@
       <c r="AB52" s="5"/>
       <c r="AC52" s="6"/>
       <c r="AD52" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="AP52" s="6"/>
     </row>
@@ -9436,7 +10151,7 @@
       <c r="AB53" s="5"/>
       <c r="AC53" s="6"/>
       <c r="AD53" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="AP53" s="6"/>
     </row>
@@ -9462,7 +10177,7 @@
       <c r="AA55" s="6"/>
       <c r="AB55" s="5"/>
       <c r="AC55" s="6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="AP55" s="6"/>
     </row>
@@ -9477,7 +10192,7 @@
       <c r="AB56" s="5"/>
       <c r="AC56" s="6"/>
       <c r="AD56" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="AP56" s="6"/>
     </row>
@@ -9510,7 +10225,7 @@
       <c r="P59" s="6"/>
       <c r="Q59" s="5"/>
       <c r="R59" s="6" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="AA59" s="6"/>
       <c r="AP59" s="6"/>
@@ -9521,8 +10236,8 @@
       <c r="J60" s="6"/>
       <c r="P60" s="6"/>
       <c r="Q60" s="5"/>
-      <c r="R60" s="37" t="s">
-        <v>111</v>
+      <c r="R60" s="34" t="s">
+        <v>103</v>
       </c>
       <c r="AA60" s="6"/>
       <c r="AP60" s="6"/>
@@ -9544,7 +10259,7 @@
       <c r="P62" s="6"/>
       <c r="Q62" s="7"/>
       <c r="R62" s="9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AA62" s="6"/>
       <c r="AP62" s="6"/>
@@ -9569,10 +10284,10 @@
       <c r="H65" s="6"/>
       <c r="I65" s="5"/>
       <c r="J65" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="AA65" s="6"/>
       <c r="AP65" s="6"/>
@@ -9607,7 +10322,7 @@
       <c r="P68" s="6"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="AA68" s="6"/>
       <c r="AP68" s="6"/>
@@ -9619,7 +10334,7 @@
       <c r="P69" s="6"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="6" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="AA69" s="6"/>
       <c r="AP69" s="6"/>
@@ -9632,11 +10347,11 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="6"/>
       <c r="S70" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="AA70" s="6"/>
       <c r="AP70" s="6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="8:65">
@@ -9653,7 +10368,7 @@
       <c r="AS71" s="11"/>
       <c r="AT71" s="12"/>
     </row>
-    <row r="72" spans="8:65" ht="15.75" thickBot="1">
+    <row r="72" spans="8:65" ht="15" thickBot="1">
       <c r="H72" s="6"/>
       <c r="I72" s="5"/>
       <c r="J72" s="6"/>
@@ -9676,16 +10391,16 @@
       <c r="AP73" s="6"/>
       <c r="AQ73" s="5"/>
       <c r="AR73" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="BH73" s="64" t="s">
-        <v>136</v>
-      </c>
-      <c r="BI73" s="65"/>
-      <c r="BJ73" s="65"/>
-      <c r="BK73" s="65"/>
-      <c r="BL73" s="65"/>
-      <c r="BM73" s="66"/>
+        <v>108</v>
+      </c>
+      <c r="BH73" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="BI73" s="62"/>
+      <c r="BJ73" s="62"/>
+      <c r="BK73" s="62"/>
+      <c r="BL73" s="62"/>
+      <c r="BM73" s="63"/>
     </row>
     <row r="74" spans="8:65">
       <c r="H74" s="6"/>
@@ -9716,7 +10431,7 @@
       <c r="P76" s="6"/>
       <c r="Q76" s="1"/>
       <c r="R76" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="AA76" s="6"/>
       <c r="AP76" s="6"/>
@@ -9728,7 +10443,7 @@
       <c r="P77" s="6"/>
       <c r="Q77" s="1"/>
       <c r="S77" s="6" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="AA77" s="6"/>
       <c r="AP77" s="6"/>
@@ -9741,7 +10456,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="6"/>
       <c r="S78" s="1" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA78" s="6"/>
       <c r="AP78" s="6"/>
@@ -9754,11 +10469,11 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="6"/>
       <c r="S79" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="AA79" s="6"/>
       <c r="AP79" s="6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="8:65">
@@ -9798,7 +10513,7 @@
       <c r="AP82" s="6"/>
       <c r="AQ82" s="5"/>
       <c r="AR82" s="6" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="83" spans="1:44">
@@ -9847,85 +10562,85 @@
       <c r="H88" s="6"/>
       <c r="P88" s="6"/>
       <c r="V88" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="AA88" s="6"/>
       <c r="AP88" s="6"/>
     </row>
-    <row r="89" spans="1:44" ht="15.75" thickBot="1"/>
-    <row r="90" spans="1:44" s="83" customFormat="1" ht="21.75" thickBot="1">
-      <c r="A90" s="82"/>
-      <c r="B90" s="84" t="s">
-        <v>181</v>
+    <row r="89" spans="1:44" ht="15" thickBot="1"/>
+    <row r="90" spans="1:44" s="80" customFormat="1" ht="21" thickBot="1">
+      <c r="A90" s="79"/>
+      <c r="B90" s="81" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:44" ht="26.25">
-      <c r="B92" s="85" t="s">
-        <v>171</v>
+      <c r="B92" s="82" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="93" spans="1:44" ht="21">
-      <c r="B93" s="87" t="s">
-        <v>183</v>
+      <c r="B93" s="84" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="94" spans="1:44">
       <c r="B94" s="17"/>
       <c r="C94" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="95" spans="1:44">
       <c r="D95" s="21" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:44">
       <c r="D96" s="21" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="97" spans="2:4">
       <c r="D97" s="21" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="98" spans="2:4">
       <c r="D98" s="21" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="D99" s="21" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="2:4" ht="16.5">
       <c r="B100" s="18" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="101" spans="2:4">
       <c r="B101" s="17"/>
     </row>
     <row r="102" spans="2:4" ht="21">
-      <c r="B102" s="87" t="s">
-        <v>177</v>
+      <c r="B102" s="84" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="103" spans="2:4" ht="16.5">
       <c r="B103" s="20" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="104" spans="2:4" ht="16.5">
       <c r="B104" s="20" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="105" spans="2:4" ht="16.5">
       <c r="B105" s="20" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="2:4">
@@ -9941,13 +10656,13 @@
       <c r="B109" s="20"/>
     </row>
     <row r="110" spans="2:4">
-      <c r="B110" s="86"/>
+      <c r="B110" s="83"/>
     </row>
     <row r="111" spans="2:4">
-      <c r="B111" s="86"/>
+      <c r="B111" s="83"/>
     </row>
     <row r="112" spans="2:4">
-      <c r="B112" s="86"/>
+      <c r="B112" s="83"/>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" s="17"/>
@@ -9966,11 +10681,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:AY57"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="2" spans="1:51" ht="23.25">
-      <c r="B2" s="68" t="s">
-        <v>139</v>
+      <c r="B2" s="65" t="s">
+        <v>131</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9995,8 +10710,8 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="4"/>
-      <c r="AA2" s="68" t="s">
-        <v>147</v>
+      <c r="AA2" s="65" t="s">
+        <v>139</v>
       </c>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
@@ -10023,79 +10738,79 @@
       <c r="AX2" s="3"/>
       <c r="AY2" s="4"/>
     </row>
-    <row r="3" spans="1:51">
-      <c r="B3" s="72" t="s">
+    <row r="3" spans="1:51" ht="15">
+      <c r="B3" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y3" s="6"/>
+      <c r="AA3" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="Y3" s="6"/>
-      <c r="AA3" s="69" t="s">
-        <v>148</v>
-      </c>
       <c r="AY3" s="6"/>
     </row>
-    <row r="4" spans="1:51">
-      <c r="B4" s="73" t="s">
+    <row r="4" spans="1:51" ht="15">
+      <c r="B4" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y4" s="6"/>
+      <c r="AA4" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="Y4" s="6"/>
-      <c r="AA4" s="69" t="s">
-        <v>149</v>
-      </c>
       <c r="AY4" s="6"/>
     </row>
-    <row r="5" spans="1:51">
-      <c r="B5" s="73" t="s">
+    <row r="5" spans="1:51" ht="15">
+      <c r="B5" s="70" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y5" s="6"/>
+      <c r="AA5" s="66" t="s">
         <v>142</v>
       </c>
-      <c r="Y5" s="6"/>
-      <c r="AA5" s="69" t="s">
-        <v>150</v>
-      </c>
       <c r="AY5" s="6"/>
     </row>
-    <row r="6" spans="1:51">
-      <c r="B6" s="73" t="s">
+    <row r="6" spans="1:51" ht="15">
+      <c r="B6" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y6" s="6"/>
+      <c r="AA6" s="66" t="s">
         <v>143</v>
       </c>
-      <c r="Y6" s="6"/>
-      <c r="AA6" s="69" t="s">
-        <v>151</v>
-      </c>
       <c r="AY6" s="6"/>
     </row>
-    <row r="7" spans="1:51">
-      <c r="B7" s="72" t="s">
+    <row r="7" spans="1:51" ht="15">
+      <c r="B7" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y7" s="6"/>
+      <c r="AA7" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="Y7" s="6"/>
-      <c r="AA7" s="70" t="s">
-        <v>152</v>
-      </c>
       <c r="AY7" s="6"/>
     </row>
     <row r="8" spans="1:51">
-      <c r="B8" s="73" t="s">
+      <c r="B8" s="70" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y8" s="6"/>
+      <c r="AA8" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="Y8" s="6"/>
-      <c r="AA8" s="71" t="s">
-        <v>153</v>
-      </c>
       <c r="AY8" s="6"/>
     </row>
     <row r="9" spans="1:51">
-      <c r="B9" s="73" t="s">
+      <c r="B9" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y9" s="6"/>
+      <c r="AA9" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="Y9" s="6"/>
-      <c r="AA9" s="70" t="s">
-        <v>154</v>
-      </c>
       <c r="AY9" s="6"/>
     </row>
     <row r="10" spans="1:51">
-      <c r="B10" s="81" t="s">
-        <v>170</v>
+      <c r="B10" s="78" t="s">
+        <v>162</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -10146,59 +10861,59 @@
       <c r="AX10" s="8"/>
       <c r="AY10" s="9"/>
     </row>
-    <row r="12" spans="1:51">
-      <c r="B12" s="67" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:51" ht="15.75" thickBot="1"/>
-    <row r="14" spans="1:51" s="65" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A14" s="74"/>
-      <c r="B14" s="75" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" spans="1:51" ht="15.75" thickBot="1"/>
-    <row r="16" spans="1:51" ht="15.75" thickBot="1">
-      <c r="C16" s="76" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="77"/>
-      <c r="M16" s="77"/>
-      <c r="N16" s="77"/>
-      <c r="O16" s="78"/>
+    <row r="12" spans="1:51" ht="15">
+      <c r="B12" s="64" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" ht="15" thickBot="1"/>
+    <row r="14" spans="1:51" s="62" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A14" s="71"/>
+      <c r="B14" s="72" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" ht="15" thickBot="1"/>
+    <row r="16" spans="1:51" ht="15" thickBot="1">
+      <c r="C16" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="74"/>
+      <c r="L16" s="74"/>
+      <c r="M16" s="74"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="75"/>
     </row>
     <row r="18" spans="4:29">
       <c r="D18" s="10"/>
       <c r="E18" s="11" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
-      <c r="P18" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q18" s="89"/>
-      <c r="R18" s="89"/>
-      <c r="S18" s="89"/>
-      <c r="T18" s="89"/>
-      <c r="U18" s="90"/>
-      <c r="X18" s="88" t="s">
-        <v>161</v>
-      </c>
-      <c r="Y18" s="89"/>
-      <c r="Z18" s="89"/>
-      <c r="AA18" s="90"/>
+      <c r="P18" s="85" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q18" s="86"/>
+      <c r="R18" s="86"/>
+      <c r="S18" s="86"/>
+      <c r="T18" s="86"/>
+      <c r="U18" s="87"/>
+      <c r="X18" s="85" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y18" s="86"/>
+      <c r="Z18" s="86"/>
+      <c r="AA18" s="87"/>
     </row>
     <row r="19" spans="4:29">
       <c r="F19" s="4"/>
@@ -10207,7 +10922,7 @@
     </row>
     <row r="20" spans="4:29">
       <c r="F20" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="R20" s="6"/>
       <c r="Y20" s="6"/>
@@ -10215,7 +10930,7 @@
     <row r="21" spans="4:29">
       <c r="F21" s="6"/>
       <c r="G21" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="R21" s="6"/>
       <c r="Y21" s="6"/>
@@ -10238,15 +10953,15 @@
     <row r="24" spans="4:29">
       <c r="F24" s="6"/>
       <c r="H24" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="R24" s="6"/>
       <c r="Y24" s="6"/>
     </row>
     <row r="25" spans="4:29">
       <c r="F25" s="6"/>
-      <c r="H25" s="37" t="s">
-        <v>138</v>
+      <c r="H25" s="34" t="s">
+        <v>130</v>
       </c>
       <c r="R25" s="6"/>
       <c r="Y25" s="6"/>
@@ -10272,10 +10987,10 @@
       <c r="F28" s="6"/>
       <c r="H28" s="6"/>
       <c r="J28" s="6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="Y28" s="6"/>
     </row>
@@ -10306,10 +11021,10 @@
       <c r="R31" s="6"/>
       <c r="S31" s="5"/>
       <c r="T31" s="6" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="Y31" s="6" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="4:29">
@@ -10340,7 +11055,7 @@
       <c r="R34" s="6"/>
       <c r="Y34" s="6"/>
       <c r="AA34" s="6" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="6:33">
@@ -10358,7 +11073,7 @@
       <c r="R36" s="6"/>
       <c r="Y36" s="6"/>
       <c r="AA36" s="6" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="37" spans="6:33">
@@ -10390,7 +11105,7 @@
       <c r="Y39" s="6"/>
       <c r="AA39" s="6"/>
       <c r="AC39" s="6" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="6:33">
@@ -10410,7 +11125,7 @@
       <c r="Y41" s="6"/>
       <c r="AA41" s="6"/>
       <c r="AC41" s="6" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="6:33">
@@ -10445,7 +11160,7 @@
       <c r="AA44" s="6"/>
       <c r="AC44" s="6"/>
       <c r="AE44" s="6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="6:33">
@@ -10457,9 +11172,9 @@
       <c r="AA45" s="6"/>
       <c r="AC45" s="6"/>
       <c r="AE45" s="6"/>
-      <c r="AF45" s="79"/>
-      <c r="AG45" s="80" t="s">
-        <v>169</v>
+      <c r="AF45" s="76"/>
+      <c r="AG45" s="77" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="6:33">
@@ -10479,7 +11194,7 @@
       <c r="Y47" s="6"/>
       <c r="AA47" s="6"/>
       <c r="AC47" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="6:33">
@@ -10535,7 +11250,7 @@
       <c r="Y53" s="6"/>
       <c r="AA53" s="6"/>
       <c r="AC53" s="6"/>
-      <c r="AO53" s="79"/>
+      <c r="AO53" s="76"/>
     </row>
     <row r="54" spans="6:41">
       <c r="F54" s="6"/>
@@ -10586,86 +11301,86 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C2:C17"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="3:3">
       <c r="C3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="3:3">
       <c r="C4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="3:3">
       <c r="C14" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="3:3">
       <c r="C15" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="3:3">
       <c r="C16" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
